--- a/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1892 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:DW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>OA5YizjL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GvRRSA15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>aymes jeremy</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CI9LnrCi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>saintini nathanael</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>bw41ww90</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>morante leandro</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>K6gqRt3c</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>falette simon</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6c3rD50k</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>djaha akim</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>KAGdlKQ8</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bamba mohamed</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>hOVOETub</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>siby mahame</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>zciOF0Jn</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>amraoui ayoub</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>jFzgBj16</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ouotro patrick</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AuRgvOVQ</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>robin milan</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0MPqros3</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>mendy oucasse</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>fkOg2Gqj</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>mvogo yvon</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Est8UaLc</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>igor silva</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>bLU8KtEd</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>talbi montassar</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>4nPjVrMS</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>mendy formose</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>zTOOlq65</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>aiyegun tosin</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>YJhgLOwk</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>ponceau julien</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>O2h5w23g</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>ngameni darline zidane</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>WzrmHcCA</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>abergel laurent</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>pOt3Q6yb</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>pagis pablo</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>ba2ejA41</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>dieng bamba cheikh dieng</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>8vMxrdie</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>mvuka joel</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>8GM9rzEp</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>belloumou samir</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>fuqL2LJ2</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>bonalair max</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>tvNblrMr</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>diawara abdoul</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>GM3MZsvr</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>etile yannick</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Yye7kYuP</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>gautier luan</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>xA5oIAIk</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>ipiele alain</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>xrsWhgRE</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>ebong arthur</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>GjVTxPsc</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>james isaac</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>hbh3pcUj</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>kalulu gedeon</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>fHMXip22</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>kroupi eli junior</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>p6J3hnvC</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>le bris theo</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>KAxiV8Bj</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>leroy benjamin</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>YByvtrWm</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>soumano sambou</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>xA5oIAIk</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>ipiele alain</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>xA5oIAIk</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>ipiele alain</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>6c3rD50k</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>djaha akim</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>tvNblrMr</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>diawara abdoul</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>tvNblrMr</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>diawara abdoul</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>0MPqros3</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>mendy oucasse</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>8GM9rzEp</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>belloumou samir</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>8GM9rzEp</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>belloumou samir</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>hOVOETub</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>siby mahame</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>jFzgBj16</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>ouotro patrick</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>xrsWhgRE</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>ebong arthur</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>xrsWhgRE</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>ebong arthur</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>pOt3Q6yb</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>pagis pablo</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>YByvtrWm</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>soumano sambou</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>YByvtrWm</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>soumano sambou</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>ba2ejA41</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>dieng bamba cheikh dieng</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>fHMXip22</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>kroupi eli junior</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>fHMXip22</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>kroupi eli junior</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>zTOOlq65</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>aiyegun tosin</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>p6J3hnvC</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>le bris theo</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>p6J3hnvC</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>le bris theo</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>YJhgLOwk</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>ponceau julien</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>lEQmcVR0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tCw122Zu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>oukidja alexandre</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ncoSpPJ3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>kouao koffi</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>O8reaWmD</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>sane sadibou</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>jZhhxxLu</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>traore ismael</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>21NXX0AU</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>cande fali</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>tE85H9db</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>nduquidi joseph</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GlPxp8Ek</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>deminguet jessy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>E5Ot0kk3</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>sabaly cheikh tidiane</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>OKRPP19G</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>jallow ablie</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>v9UFU7UB</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>sane ibou</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>06rZTKMc</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>hein gauthier</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>hz9iLSns</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>placide johnny</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>O4n6NMUE</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>meynadier tom</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>SGS1GzV5</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>akueson gustave</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>4C2mjUxk</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>roncaglia anthony</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>dGEFacR1</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>bohnert florian</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>EodMM41U</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vincent christophe</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ronEz0Iq</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>ducrocq tom</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>b9dIWhMU</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>onana cyrille</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>pfhFEyG5</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>tomi felix</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>zs0YOeUm</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>bianchini florian</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>vVf0mSM7</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>boutrah amine</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>Y3ooARhm</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>atta arthur</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>UqhfTgL6</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>bokele mputu morgan</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>YaVQrOB5</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>colin maxime</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>W6Zv9LTG</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>abou lo</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>CYlmgaU3</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>mbaye malick</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>OADbJzj2</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>sy pape</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>EX50xRu9</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>toure alpha</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>tIMjIu1I</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>ariss zakaria</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>OdiG9Lyg</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>fabri julien</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>IwWAp1LB</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>guevara juan</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0hzAGETn</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>janneh jocelyn</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>S8afnvrC</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>maggiotti julien</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>xr3SdJz4</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>rodrigues clement</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0f89SvvA</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>tramoni lisandru</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>Y3ooARhm</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>atta arthur</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>Y3ooARhm</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>atta arthur</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>tE85H9db</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>nduquidi joseph</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>YaVQrOB5</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>colin maxime</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>YaVQrOB5</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>colin maxime</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>ncoSpPJ3</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>kouao koffi</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>EX50xRu9</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>toure alpha</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>EX50xRu9</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>toure alpha</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>21NXX0AU</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>cande fali</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>UqhfTgL6</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>bokele mputu morgan</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>UqhfTgL6</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>bokele mputu morgan</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>E5Ot0kk3</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>sabaly cheikh tidiane</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>tIMjIu1I</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>ariss zakaria</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>tIMjIu1I</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>ariss zakaria</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>O4n6NMUE</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>meynadier tom</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>0hzAGETn</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>janneh jocelyn</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>0hzAGETn</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>janneh jocelyn</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>b9dIWhMU</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>onana cyrille</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>xr3SdJz4</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>rodrigues clement</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>xr3SdJz4</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>rodrigues clement</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>zs0YOeUm</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>bianchini florian</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>0f89SvvA</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>tramoni lisandru</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>0f89SvvA</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>tramoni lisandru</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>EodMM41U</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>vincent christophe</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>IwWAp1LB</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>guevara juan</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>IwWAp1LB</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>guevara juan</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>pfhFEyG5</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>tomi felix</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1439 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:EM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IH9cf1NH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>larsonneur gautier</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>tAIHMBhs</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>nzuzi marwann</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>QcLd3bL1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>batubinsika dylan</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>OYtRcGFm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>abdelhamid yunis</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>by5QHeY8</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>macon yvann</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>S0fUJqv9</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>tardieu florian</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>fkTUaOi8</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>davitashvili zuriko</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4MoD7F1A</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>old benjamin</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>W6Xd8Gyg</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>amougou mathis</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>dKzjZfiI</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>cafaro mathieu</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>MDGbgDq7</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>sissoko ibrahim</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>xMzvOmz3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>desmas arthur</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Spy29tSF</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>nego loic</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>lGwSlg7D</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>sangante arouna</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>WvnBSOGB</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>youte kinkoue etienne</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>pMUGrcL4</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>lloris gautier</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>v9ih1MV1</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>zouaoui yanis</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>21pKzBVs</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>kechta yassine</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>ULZGhzIc</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>targhalline oussama</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>jDX28pzf</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>toure abdoulaye</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>n5pKaQsh</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>joujou antoine</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>A3L0pzbI</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>casimir josue</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>W6PE7nsb</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>aiki ayman</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2acUGEci</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>appiah dennis</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>lp6kCEjc</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>boakye augustine</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0SDVC1gR</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>fomba lamine</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>GGYnig7m</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>maubleu brice</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>tArngh4I</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>mouton louis</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>SG64s4Ks</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>nade mickael</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>EHROMJfq</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>owusu beres</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>4pLzmm2C</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>bouneb ismael</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>jevYFpy7</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>gorgelin mathieu</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>E7LMto5e</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>grandsir samuel</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>AgmwPJ36</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>kuzyayev daler</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>6H79Cl3d</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>mosengo daren nbenbege</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>2Lq1p0u3</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>ndiaye rassoul</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0UjafPph</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>sabbi emmanuel</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>hpstm6bQ</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>salmier yoann</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>futJjw50</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>soumare issa</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>2acUGEci</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>appiah dennis</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>2acUGEci</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>appiah dennis</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>tAIHMBhs</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>nzuzi marwann</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>tArngh4I</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>mouton louis</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>tArngh4I</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>mouton louis</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>fkTUaOi8</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>davitashvili zuriko</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>lp6kCEjc</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>boakye augustine</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>lp6kCEjc</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>boakye augustine</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>S0fUJqv9</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>tardieu florian</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>vswx9zEb</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>wadji ibrahima</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>MDGbgDq7</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>sissoko ibrahim</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>W6PE7nsb</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>aiki ayman</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>W6PE7nsb</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>aiki ayman</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>4MoD7F1A</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>old benjamin</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>2Lq1p0u3</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>ndiaye rassoul</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>2Lq1p0u3</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>ndiaye rassoul</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>A3L0pzbI</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>casimir josue</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>0UjafPph</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>sabbi emmanuel</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>0UjafPph</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>sabbi emmanuel</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>lGwSlg7D</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>sangante arouna</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>futJjw50</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>soumare issa</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>futJjw50</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>soumare issa</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>ULZGhzIc</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>targhalline oussama</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>hpstm6bQ</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>salmier yoann</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>hpstm6bQ</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>salmier yoann</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>v9ih1MV1</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>zouaoui yanis</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>E7LMto5e</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>grandsir samuel</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>E7LMto5e</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>grandsir samuel</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>21pKzBVs</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>kechta yassine</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,2108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:EU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>rcbM0Dd8</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rulli geronimo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>rNLU0jIl</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>murillo michael</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OYrb8EBS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>balerdi leonardo</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>8YhWSbAS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>brassier lilian</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>tvuaMWgc</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>merlin quentin</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>nZs03zT2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>kondogbia geoffrey</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ITwS8wMo</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>hojbjerg pierre emile</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>hxe108Jl</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>greenwood mason</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>lxSgSRDd</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>harit amine</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>dU3VTnID</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>luis henrique</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>8jdHWf50</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>wahi sepe elye</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>xCg7OFVE</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>diouf yehvann</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>W2ZQhrQI</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>sangui nhoa</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>zBgW9dak</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>okumu joseph</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>fRbu2Opo</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>agbadou emmanuel</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>4nBZRS2T</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>akieme sergio</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2LonY10K</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>munetsi nyasha</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>MskdO4tG</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>atangana edoa valentin</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Yg2zH6de</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>fofana yaya kader</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>j9vuLu2S</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>junya ito</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>jeOb1FYh</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>diakite oumar</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>ttEUhyfq</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>nakamura keito</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>6whb8Ahe</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>seghir salim</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Wvb8v5p5</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>cornelius derek</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>GGTSMhui</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>de lange jeffrey</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>dYFeVggU</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>lirola pol</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>xbLpmH22</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>meite abdoul</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>pQEvn0aK</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>rongier valentin</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>WQQaRzMF</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>rowe jon</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>YZTn9sgp</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>sternal enzo</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>42xsAKpa</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>adeline martin</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>vBVl3fPN</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>bojang adama</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>WfOJXqJA</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>de smet thibault</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>hhMsOIeH</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>diakhon mamadou</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>YywLL7YO</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>gabriel moscardo</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>tSf0YZjE</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>khadra reda</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>Eol9RH7r</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>kipre cedric</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>EyJTU6I9</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>olliero alexandre</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>8fTnn97m</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>salama amine</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>WQQaRzMF</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>rowe jon</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>WQQaRzMF</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>rowe jon</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>8jdHWf50</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>wahi sepe elye</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>lxSgSRDd</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>harit amine</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>42xsAKpa</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>adeline martin</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>42xsAKpa</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>adeline martin</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>Yg2zH6de</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>fofana yaya kader</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>8fTnn97m</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>salama amine</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>8fTnn97m</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>salama amine</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>jeOb1FYh</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>diakite oumar</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>Eol9RH7r</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>kipre cedric</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Eol9RH7r</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>kipre cedric</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>ttEUhyfq</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>nakamura keito</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>hhMsOIeH</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>diakhon mamadou</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>hhMsOIeH</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>diakhon mamadou</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>j9vuLu2S</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>junya ito</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>MkgjOoBG</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>kone ismael</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>jXMIit0S</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>moumbagna faris</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>63FSiIkD</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>daramy mohammed</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr"/>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
+      <c r="EK2" t="inlineStr"/>
+      <c r="EL2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr"/>
+      <c r="EO2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr"/>
+      <c r="ER2" t="inlineStr"/>
+      <c r="ES2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>0pvInj5s</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dl7hEyx3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>beunardeau quentin</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bD4oBeZu</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>danger bradlay</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>WEf5zAtn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>mendy bissenty</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CjerQdJC</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>kouagba loic</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bDfdmD9h</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>doucoure fode</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>zkh2UjHb</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>eickmayer joachim</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>xbSVpTij</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>renel samuel</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Cf8ju4GK</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>hachem ryad</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>lUS5czaO</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>ifnaoui merwan</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>xATlu4A5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>benali hacene</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>tYd2ZZ4l</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>durand damien</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4nR8LCCp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>sollacaro francois</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>d4NLQlPJ</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>youssouf mohamed</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>j1uZ9TzE</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ayessa jesah</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>tWEjLiqi</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>bamba axel</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>4xeKQf0n</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>strata tony</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>xtTKOiHO</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>jacob valentin</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>4Ug33NLF</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>anziani julien</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>Otvrow2g</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>barreto mickael</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>S8m3Z0Ec</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>touzghar yoann</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>GfQuApsR</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>ibayi christopher</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>G4gI1g5M</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>badji aliou</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>EeeUoqnD</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>bonet pepe</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eqg3ERA3</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>botella ivann</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>l0CB1r2R</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>dembi fred</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>MT98e48G</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>jabol folcarelli tim</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>lMOq4ljm</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>mangani thomas</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>trRNdJLg</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>quemper stephen</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>25CTGXNp</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>quilichini ghjuvanni</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>ptT4ile8</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>toure al hassan</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>dfsrq39I</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>vidal clement</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>l0CB1r2R</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>dembi fred</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>l0CB1r2R</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>dembi fred</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>zkh2UjHb</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>eickmayer joachim</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>G4gI1g5M</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>badji aliou</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>G4gI1g5M</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>badji aliou</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>tYd2ZZ4l</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>durand damien</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>MT98e48G</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>jabol folcarelli tim</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>MT98e48G</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>jabol folcarelli tim</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>ptT4ile8</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>toure al hassan</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>ptT4ile8</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>toure al hassan</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>xtTKOiHO</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>jacob valentin</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>GfQuApsR</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>ibayi christopher</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>dfsrq39I</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>vidal clement</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>dfsrq39I</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>vidal clement</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>tWEjLiqi</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>bamba axel</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>bDfdmD9h</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>doucoure fode</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>xbSVpTij</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>renel samuel</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>WEf5zAtn</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>mendy bissenty</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>lMOq4ljm</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>mangani thomas</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr">
+        <is>
+          <t>lMOq4ljm</t>
+        </is>
+      </c>
+      <c r="ES3" t="inlineStr">
+        <is>
+          <t>mangani thomas</t>
+        </is>
+      </c>
+      <c r="ET3" t="inlineStr">
+        <is>
+          <t>4Ug33NLF</t>
+        </is>
+      </c>
+      <c r="EU3" t="inlineStr">
+        <is>
+          <t>anziani julien</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU3"/>
+  <dimension ref="A1:EU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,949 +891,1021 @@
       </c>
       <c r="CP1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_enter_away_1</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_1</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_2</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_2</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_3</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_3</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_4</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_4</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_5</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_5</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_6</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_6</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_7</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_7</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_8</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_8</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_9</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_9</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_10</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_10</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_11</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_11</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_12</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_12</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_1</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_1</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_7</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_8</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_9</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_10</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_11</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_12</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_13</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_13</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_14</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_14</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_home_15</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_13</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_15</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>rcbM0Dd8</t>
+          <t>2qYBqH5q</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rulli geronimo</t>
+          <t>lucas perri</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rNLU0jIl</t>
+          <t>6PvHspma</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>murillo michael</t>
+          <t>clinton mata</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OYrb8EBS</t>
+          <t>K44QNA2A</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>balerdi leonardo</t>
+          <t>caleta car duje</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8YhWSbAS</t>
+          <t>tdnibGHH</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>brassier lilian</t>
+          <t>niakhate moussa</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>tvuaMWgc</t>
+          <t>0U8JJaVd</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>merlin quentin</t>
+          <t>caqueret maxence</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>nZs03zT2</t>
+          <t>Kty10JVG</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>kondogbia geoffrey</t>
+          <t>matic nemanja</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ITwS8wMo</t>
+          <t>hQOIoFOs</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>hojbjerg pierre emile</t>
+          <t>tolisso corentin</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>hxe108Jl</t>
+          <t>CnBQp2sj</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>greenwood mason</t>
+          <t>maitland niles ainsley</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>lxSgSRDd</t>
+          <t>CCz5z9Ug</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>harit amine</t>
+          <t>abner</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dU3VTnID</t>
+          <t>QgN9t9CH</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>luis henrique</t>
+          <t>mikautadze georges</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>8jdHWf50</t>
+          <t>YegtWFr9</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>wahi sepe elye</t>
+          <t>lacazette alexandre</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>xCg7OFVE</t>
+          <t>4zY3gbw3</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>diouf yehvann</t>
+          <t>johnsson karl johan</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>W2ZQhrQI</t>
+          <t>vg3drc4E</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>sangui nhoa</t>
+          <t>doue guela</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>zBgW9dak</t>
+          <t>GIuyQQam</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>okumu joseph</t>
+          <t>sow saidou</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>fRbu2Opo</t>
+          <t>lOBSekrn</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>agbadou emmanuel</t>
+          <t>sylla abakar</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>4nBZRS2T</t>
+          <t>x4JfNzq1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>akieme sergio</t>
+          <t>bakwa dilane</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2LonY10K</t>
+          <t>vDrVnIrd</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>munetsi nyasha</t>
+          <t>andrey santos</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>MskdO4tG</t>
+          <t>nHtBqog0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>atangana edoa valentin</t>
+          <t>doukoure ismael</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Yg2zH6de</t>
+          <t>dIkk2y21</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>fofana yaya kader</t>
+          <t>nanasi sebastian</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>j9vuLu2S</t>
+          <t>bPoOcxvJ</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>junya ito</t>
+          <t>lemarechal felix</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>jeOb1FYh</t>
+          <t>nFakLd1E</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>diakite oumar</t>
+          <t>diarra habib</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>ttEUhyfq</t>
+          <t>by8Xcffd</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>nakamura keito</t>
+          <t>emegha emanuel</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>6whb8Ahe</t>
+          <t>Qc9B0Q23</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>seghir salim</t>
+          <t>adryelson</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0S6Hz5ji</t>
+          <t>Qyrn555R</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>carboni valentin</t>
+          <t>benrahma said</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Wvb8v5p5</t>
+          <t>0IG1JXBr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>cornelius derek</t>
+          <t>descamps remy</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>GGTSMhui</t>
+          <t>WG2O5tgf</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>de lange jeffrey</t>
+          <t>diawara mahamadou</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>dYFeVggU</t>
+          <t>6N65iDOI</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>lirola pol</t>
+          <t>fofana malick</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>xbLpmH22</t>
+          <t>vaX5DmSc</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>meite abdoul</t>
+          <t>kumbedi sael</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>pQEvn0aK</t>
+          <t>I3i2lcHS</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>rongier valentin</t>
+          <t>molebe enzo</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>WQQaRzMF</t>
+          <t>K8mhV4Es</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>rowe jon</t>
+          <t>gift emmanuel</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>YZTn9sgp</t>
+          <t>WjEvCrvs</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>sternal enzo</t>
+          <t>tessmann tanner</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>42xsAKpa</t>
+          <t>AV5YKO71</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>adeline martin</t>
+          <t>diongu daouda</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>vBVl3fPN</t>
+          <t>M1dogGtP</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>bojang adama</t>
+          <t>fila karol</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>WfOJXqJA</t>
+          <t>WUXGmxoa</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>de smet thibault</t>
+          <t>mara sekou</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>hhMsOIeH</t>
+          <t>0QNoKs1B</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>diakhon mamadou</t>
+          <t>moreira diego</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>YywLL7YO</t>
+          <t>dta4FB8P</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>gabriel moscardo</t>
+          <t>mwanga junior</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>tSf0YZjE</t>
+          <t>zHRwZwXF</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>khadra reda</t>
+          <t>risser robin</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>Eol9RH7r</t>
+          <t>Op4InIJ1</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>kipre cedric</t>
+          <t>sebas jeremy</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>EyJTU6I9</t>
+          <t>YFqLAlLI</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>olliero alexandre</t>
+          <t>senaya marvin</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>8fTnn97m</t>
+          <t>ARPvetaS</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>salama amine</t>
+          <t>wiley caleb</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>WQQaRzMF</t>
+          <t>6N65iDOI</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>rowe jon</t>
+          <t>fofana malick</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>WQQaRzMF</t>
+          <t>6N65iDOI</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>rowe jon</t>
+          <t>fofana malick</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>8jdHWf50</t>
+          <t>QgN9t9CH</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>wahi sepe elye</t>
+          <t>mikautadze georges</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0S6Hz5ji</t>
+          <t>K8mhV4Es</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>carboni valentin</t>
+          <t>gift emmanuel</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0S6Hz5ji</t>
+          <t>K8mhV4Es</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>carboni valentin</t>
+          <t>gift emmanuel</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>lxSgSRDd</t>
+          <t>CCz5z9Ug</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>harit amine</t>
+          <t>abner</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>42xsAKpa</t>
+          <t>WjEvCrvs</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>adeline martin</t>
+          <t>tessmann tanner</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>42xsAKpa</t>
+          <t>WjEvCrvs</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>adeline martin</t>
+          <t>tessmann tanner</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>Yg2zH6de</t>
+          <t>Kty10JVG</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>fofana yaya kader</t>
+          <t>matic nemanja</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>8fTnn97m</t>
+          <t>Qc9B0Q23</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>salama amine</t>
+          <t>adryelson</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>8fTnn97m</t>
+          <t>Qc9B0Q23</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>salama amine</t>
+          <t>adryelson</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>jeOb1FYh</t>
+          <t>K44QNA2A</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>diakite oumar</t>
+          <t>caleta car duje</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>Eol9RH7r</t>
+          <t>ARPvetaS</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>kipre cedric</t>
+          <t>wiley caleb</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>Eol9RH7r</t>
+          <t>ARPvetaS</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>kipre cedric</t>
+          <t>wiley caleb</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>ttEUhyfq</t>
+          <t>bPoOcxvJ</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>nakamura keito</t>
+          <t>lemarechal felix</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>hhMsOIeH</t>
+          <t>WUXGmxoa</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>diakhon mamadou</t>
+          <t>mara sekou</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>hhMsOIeH</t>
+          <t>WUXGmxoa</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>diakhon mamadou</t>
+          <t>mara sekou</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>j9vuLu2S</t>
+          <t>dIkk2y21</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>junya ito</t>
+          <t>nanasi sebastian</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>MkgjOoBG</t>
+          <t>YFqLAlLI</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>kone ismael</t>
+          <t>senaya marvin</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>jXMIit0S</t>
+          <t>YFqLAlLI</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>moumbagna faris</t>
+          <t>senaya marvin</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>2TItKacj</t>
+          <t>nFakLd1E</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>nadir bilal</t>
+          <t>diarra habib</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>63FSiIkD</t>
+          <t>0QNoKs1B</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>daramy mohammed</t>
+          <t>moreira diego</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>MoRIjLE2</t>
+          <t>0QNoKs1B</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>kone abdoul</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr"/>
-      <c r="DY2" t="inlineStr"/>
-      <c r="DZ2" t="inlineStr"/>
-      <c r="EA2" t="inlineStr"/>
-      <c r="EB2" t="inlineStr"/>
-      <c r="EC2" t="inlineStr"/>
-      <c r="ED2" t="inlineStr"/>
-      <c r="EE2" t="inlineStr"/>
-      <c r="EF2" t="inlineStr"/>
-      <c r="EG2" t="inlineStr"/>
-      <c r="EH2" t="inlineStr"/>
-      <c r="EI2" t="inlineStr"/>
-      <c r="EJ2" t="inlineStr"/>
-      <c r="EK2" t="inlineStr"/>
-      <c r="EL2" t="inlineStr"/>
-      <c r="EM2" t="inlineStr"/>
-      <c r="EN2" t="inlineStr"/>
-      <c r="EO2" t="inlineStr"/>
+          <t>moreira diego</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>GIuyQQam</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>sow saidou</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Op4InIJ1</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>sebas jeremy</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Op4InIJ1</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>sebas jeremy</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>by8Xcffd</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>emegha emanuel</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>rsiloRPO</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>nuamah ernest</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>jgaGiVOl</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>tagliafico nicolas</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>tvY8ZVkb</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>delaine thomas</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>rcZfwzkD</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>sahi dion</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>hjJue7Qt</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>lukovic milos</t>
+        </is>
+      </c>
       <c r="EP2" t="inlineStr"/>
       <c r="EQ2" t="inlineStr"/>
       <c r="ER2" t="inlineStr"/>
@@ -1844,297 +1916,297 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0pvInj5s</t>
+          <t>WlzDg17E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dl7hEyx3</t>
+          <t>25CTGXNp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>beunardeau quentin</t>
+          <t>quilichini ghjuvanni</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>bD4oBeZu</t>
+          <t>dfsrq39I</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>danger bradlay</t>
+          <t>vidal clement</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WEf5zAtn</t>
+          <t>j1uZ9TzE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>mendy bissenty</t>
+          <t>ayessa jesah</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CjerQdJC</t>
+          <t>4xeKQf0n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>kouagba loic</t>
+          <t>strata tony</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bDfdmD9h</t>
+          <t>tWEjLiqi</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>doucoure fode</t>
+          <t>bamba axel</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>zkh2UjHb</t>
+          <t>trRNdJLg</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>eickmayer joachim</t>
+          <t>quemper stephen</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>xbSVpTij</t>
+          <t>4Ug33NLF</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>renel samuel</t>
+          <t>anziani julien</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Cf8ju4GK</t>
+          <t>lMOq4ljm</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>hachem ryad</t>
+          <t>mangani thomas</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>lUS5czaO</t>
+          <t>MT98e48G</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ifnaoui merwan</t>
+          <t>jabol folcarelli tim</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>xATlu4A5</t>
+          <t>GfQuApsR</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>benali hacene</t>
+          <t>ibayi christopher</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>tYd2ZZ4l</t>
+          <t>CtZ04TjI</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>durand damien</t>
+          <t>soumano moussa</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4nR8LCCp</t>
+          <t>Qg47cicT</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>sollacaro francois</t>
+          <t>boucher zacharie</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>nkt4zHnF</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>boura ismael</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>63DHUXLG</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>mendes houboulang</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>UmQAaj9U</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>diaz michel</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>dEUlUsYE</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>hamdi mathis</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Ao6LMYLE</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>kante abdoulaye</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>l0bJ7sac</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>chavalerin xavier</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>jqI1zNGn</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>irie cyriaque</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>xQzrR2fm</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>m changama youssouf</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>QaynB0J3</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>said rafiki</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>dzY8Gcno</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>assoumou kouadou jaures</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>Otvrow2g</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>barreto mickael</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>fTn87CcD</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>khelifa anthony</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>WCC14cm0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>kouassi arsene</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>drNgaEBH</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>michel mathieu</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>S8m3Z0Ec</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>touzghar yoann</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>d4NLQlPJ</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>youssouf mohamed</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>j1uZ9TzE</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ayessa jesah</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>tWEjLiqi</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>bamba axel</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>4xeKQf0n</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>strata tony</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>xtTKOiHO</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>jacob valentin</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>vXAsoH78</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>puch herrantz mehdi</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>4Ug33NLF</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>anziani julien</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>Otvrow2g</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>barreto mickael</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>S8m3Z0Ec</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>touzghar yoann</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>GfQuApsR</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>ibayi christopher</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>G4gI1g5M</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>badji aliou</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>EeeUoqnD</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>bonet pepe</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Eqg3ERA3</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>botella ivann</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>l0CB1r2R</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>dembi fred</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>M13pWJRa</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>durivaux dylan</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>KhMVtudH</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>el hriti aniss</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>GpETZfpE</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>escartin josue</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr"/>
@@ -2143,72 +2215,72 @@
       <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>MT98e48G</t>
+          <t>zuiN9zaU</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>jabol folcarelli tim</t>
+          <t>ba pape ibnou</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>lMOq4ljm</t>
+          <t>AZyV3xma</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>mangani thomas</t>
+          <t>diop mouhamed</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>trRNdJLg</t>
+          <t>tdNIZmPm</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>quemper stephen</t>
+          <t>fage ryan</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>25CTGXNp</t>
+          <t>fyAli38M</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>quilichini ghjuvanni</t>
+          <t>michel corentin</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>CtZ04TjI</t>
+          <t>IHXHPyfp</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>soumano moussa</t>
+          <t>ripart renaud</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>ptT4ile8</t>
+          <t>A7Ucux61</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>toure al hassan</t>
+          <t>jean tahrat mehdi</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>dfsrq39I</t>
+          <t>QyZYJhmb</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>vidal clement</t>
+          <t>traore ibrahim</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr"/>
@@ -2217,314 +2289,4192 @@
       <c r="CC3" t="inlineStr"/>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>Otvrow2g</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>barreto mickael</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>Otvrow2g</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>barreto mickael</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>tWEjLiqi</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>bamba axel</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>S8m3Z0Ec</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>touzghar yoann</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>S8m3Z0Ec</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>touzghar yoann</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>d4NLQlPJ</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>youssouf mohamed</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>d4NLQlPJ</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>youssouf mohamed</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>4xeKQf0n</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>strata tony</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>4Ug33NLF</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>anziani julien</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>AZyV3xma</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>diop mouhamed</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>AZyV3xma</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>diop mouhamed</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>dzY8Gcno</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>assoumou kouadou jaures</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>A7Ucux61</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>jean tahrat mehdi</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>A7Ucux61</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>jean tahrat mehdi</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>jqI1zNGn</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>irie cyriaque</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>zuiN9zaU</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>ba pape ibnou</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>zuiN9zaU</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>ba pape ibnou</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>QaynB0J3</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>said rafiki</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>QyZYJhmb</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>traore ibrahim</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>QyZYJhmb</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>traore ibrahim</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>l0bJ7sac</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>chavalerin xavier</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>IHXHPyfp</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>ripart renaud</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>IHXHPyfp</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>ripart renaud</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>UmQAaj9U</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>diaz michel</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr"/>
+      <c r="EG3" t="inlineStr"/>
+      <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr"/>
+      <c r="EL3" t="inlineStr"/>
+      <c r="EM3" t="inlineStr"/>
+      <c r="EN3" t="inlineStr"/>
+      <c r="EO3" t="inlineStr"/>
+      <c r="EP3" t="inlineStr"/>
+      <c r="EQ3" t="inlineStr"/>
+      <c r="ER3" t="inlineStr"/>
+      <c r="ES3" t="inlineStr"/>
+      <c r="ET3" t="inlineStr"/>
+      <c r="EU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>IoCT4kRP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0QluvG6s</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mandrea anthony</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ojlo3DFG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vandermersch hugo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>YaDc8KUo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>diedounne debohi</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>v1nbamR8</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>thomas romain</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>487CQIYM</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>meddah daylam</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>GOdGE1cn</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>m vila yann</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6qDAkr52</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>keyremeh godson</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>nTSAxkMK</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>lebreton noe</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>OnEUHb2t</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>rajot lorenzo</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>byAFdWP0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>gomis tidiam</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>YLpVZgK4</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>le bihan mickael</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>YkTI15a3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>escales florian</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Knpb69xQ</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>kouadio julien</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>xbCaEITP</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>lajugie francois</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>AX04y31t</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>drouhin axel</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>QT6THpuf</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>delphis thibault</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>SGy9pst5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>kashi ahmed</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>611nUsKM</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>pajot vincent</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>E7gMZtT7</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>larose antoine</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>4SgLsxFe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>tiendrebeogo wendkuuni josue</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>4YOUdDQ3</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>bermont anthony</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>E1h8Ff92</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>djoco kapitbafan</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>GGxzFMB7</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>autret mathias</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>W6JaBPra</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>brahimi bilal</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>zRkxtbt5</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>clementia yannis</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>QoV6Ei8J</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>coulibaly kalifa</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>MN5RvsXp</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>mendy alexandre</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>fikV9v0s</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>milliner leo</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>IZetE3Oq</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>tavares heliohdino</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>GW9zt9yT</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>callens thomas</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>fukL0y0a</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>dago trevis</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>dGm01L6K</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>debbiche wael</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>hprvGtld</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>lemina noha</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>GIatFrPC</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>mahop moise</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>U7tAfTbA</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>ntignee goteh</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>rcTbvUIa</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>paris quentin</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>W6JaBPra</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>brahimi bilal</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>W6JaBPra</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>brahimi bilal</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>byAFdWP0</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>gomis tidiam</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>GGxzFMB7</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>autret mathias</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>GGxzFMB7</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>autret mathias</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>nTSAxkMK</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>lebreton noe</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>MN5RvsXp</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>mendy alexandre</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>MN5RvsXp</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>mendy alexandre</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>YLpVZgK4</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>le bihan mickael</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>IZetE3Oq</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>tavares heliohdino</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>IZetE3Oq</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>tavares heliohdino</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>487CQIYM</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>meddah daylam</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>GIatFrPC</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>mahop moise</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>GIatFrPC</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>mahop moise</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>4YOUdDQ3</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>bermont anthony</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>fukL0y0a</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>dago trevis</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>fukL0y0a</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>dago trevis</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>4SgLsxFe</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>tiendrebeogo wendkuuni josue</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>hprvGtld</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>lemina noha</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>hprvGtld</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>lemina noha</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>E1h8Ff92</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>djoco kapitbafan</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>U7tAfTbA</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>ntignee goteh</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>U7tAfTbA</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>ntignee goteh</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>Knpb69xQ</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>kouadio julien</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr"/>
+      <c r="EE4" t="inlineStr"/>
+      <c r="EF4" t="inlineStr"/>
+      <c r="EG4" t="inlineStr"/>
+      <c r="EH4" t="inlineStr"/>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr"/>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>QoV6Ei8J</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>coulibaly kalifa</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t>QoV6Ei8J</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
+          <t>coulibaly kalifa</t>
+        </is>
+      </c>
+      <c r="ET4" t="inlineStr">
+        <is>
+          <t>6qDAkr52</t>
+        </is>
+      </c>
+      <c r="EU4" t="inlineStr">
+        <is>
+          <t>keyremeh godson</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>zyWS0tQi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8xrw5lBb</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ndiaye massamba</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ziL9G1en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>magnin yohan</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ygx5oNQb</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>da silva damien</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>h0WK6DL4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>jacquet jeremy</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>zev04vcl</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>kabeya ethan</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2eNPn89c</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>konate cheick oumar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4fUfKBcN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ackra allan</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>nae24Rc4</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>gastien johan</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>25nL64OI</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>keita habib</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>8SNLp9tO</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>bassouamina mons</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>6BUWSZeH</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>saivet henri</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Uc1khkvm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>nkambadio obed</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>jcMPmwUo</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>tourraine mathys</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>8UK1HbMC</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>mbow mamadou</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>6Nrp053I</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>kolodziejczak timothee</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>t2wVToOG</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>ollila tuomas</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>dvCqyKNu</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>doucet lohann</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>6Ze5jFyJ</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>marchetti vincent</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>zZWv9QAr</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>camara adama</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>8zzd9I9p</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>kebbal ilan</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>MDGk7mZd</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>krasso jean philippe</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>pzIqHPOJ</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>dicko nouha</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>zJeiPqkr</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>armougom yoel</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>GfgBD9EE</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>diaby yadaly</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>xpUN168t</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>diallo baila</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>I3ygvfy8</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>diop ousmane</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>vieEUfdg</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>douane maidine</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>pQlD4dwJ</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>guivarch theo</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>hhhzfVW1</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>m bahia ivan</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>Ak6ZwNei</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>gaudin jules</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>CIHpd5Na</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>gory alimani</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>YF5m5ItO</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>kante mohamadou</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>ULOxNwXn</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>lopez julien</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>6Nb8GjF8</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>riou remy</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>C64i4xdU</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>sissoko omar</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>niLz9KKj</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>soumahoro aboubaka</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>vieEUfdg</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>douane maidine</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>vieEUfdg</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>douane maidine</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>zev04vcl</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>kabeya ethan</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>GfgBD9EE</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>diaby yadaly</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>GfgBD9EE</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>diaby yadaly</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>25nL64OI</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>keita habib</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>xpUN168t</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>diallo baila</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>xpUN168t</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>diallo baila</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>ziL9G1en</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>magnin yohan</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>I3ygvfy8</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>diop ousmane</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>I3ygvfy8</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>diop ousmane</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>8SNLp9tO</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>bassouamina mons</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>CIHpd5Na</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>gory alimani</t>
+        </is>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>CIHpd5Na</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>gory alimani</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>MDGk7mZd</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>krasso jean philippe</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>C64i4xdU</t>
+        </is>
+      </c>
+      <c r="DI5" t="inlineStr">
+        <is>
+          <t>sissoko omar</t>
+        </is>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>C64i4xdU</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>sissoko omar</t>
+        </is>
+      </c>
+      <c r="DL5" t="inlineStr">
+        <is>
+          <t>pzIqHPOJ</t>
+        </is>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>dicko nouha</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>ULOxNwXn</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>lopez julien</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>ULOxNwXn</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>lopez julien</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>dvCqyKNu</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>doucet lohann</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>niLz9KKj</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>soumahoro aboubaka</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>niLz9KKj</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>soumahoro aboubaka</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>8zzd9I9p</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>kebbal ilan</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>Ak6ZwNei</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>gaudin jules</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>Ak6ZwNei</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>gaudin jules</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>t2wVToOG</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>ollila tuomas</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr"/>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
+      <c r="EM5" t="inlineStr"/>
+      <c r="EN5" t="inlineStr"/>
+      <c r="EO5" t="inlineStr"/>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t>hhhzfVW1</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>m bahia ivan</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
+          <t>hhhzfVW1</t>
+        </is>
+      </c>
+      <c r="ES5" t="inlineStr">
+        <is>
+          <t>m bahia ivan</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>2eNPn89c</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t>konate cheick oumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>06FhaTlm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>jyzyc1pE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jaouen ewen</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GOqK3T14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>youssouf benjaloud</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CSpt7BMu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>sangante opa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>UZzd4sDM</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>sasso vincent</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8zK6oP8a</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>georgen alec</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>WSXgQK56</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bardeli enzo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>UayiGBFq</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>queiros diogo</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>6RvNumuL</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>sekongo anto</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>OrSsAkI5</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>tehan kaj</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>KQnM7QoO</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>courtet gaetan</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Kh3fmMhH</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>rivera maxence</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>pzX674k0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>mpasi nzau lionel</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>p2nsMSal</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>ngouyamsa ahmad</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>6Vz9xZIb</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>quenabio loni</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>AmGWfem4</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>mambo muzalijoma stone</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>QBWpvgXg</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>bouchouari mohamed</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>b9VtHGuL</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>younoussa wilitty</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>dfjU302n</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>mazou sacko derek</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>INSa57F7</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>taibi waniss</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Iqjtansb</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>abdallah abdel hakim</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>QqlDIsGM</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>bentayeb tawfik</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>OhP1S4nf</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>nkada timothee</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>ClAgbmjb</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>bammou yacine</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>K6JcFKeq</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>bessile loic</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>6utqVfCd</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>kone ibrahim</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>Wd8BDKWs</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>raghouber ugo</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Ue1A5pGE</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>senneville christian</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>jusUrXEa</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>skytta naatan</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2o4NnnE9</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>yassine gessime</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0SEz3Xto</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>achi bouakline mohamed</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>bokMNZhk</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>balde ibrahima</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>46NuxuYs</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>chougrani joris</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>6kl4UZvQ</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>cibois sebastien</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>rXN8qke1</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>doumbia cheick</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>tASVC4IR</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>pelon aurelien</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>pUcMCfNn</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>verdier yannis</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>2o4NnnE9</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>yassine gessime</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>2o4NnnE9</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>yassine gessime</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>OrSsAkI5</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>tehan kaj</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>Wd8BDKWs</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>raghouber ugo</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>Wd8BDKWs</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>raghouber ugo</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>6RvNumuL</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>sekongo anto</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>ClAgbmjb</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>bammou yacine</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>ClAgbmjb</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>bammou yacine</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>Kh3fmMhH</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>rivera maxence</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>Ue1A5pGE</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>senneville christian</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>Ue1A5pGE</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>senneville christian</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>8zK6oP8a</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>georgen alec</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>0SEz3Xto</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>achi bouakline mohamed</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>0SEz3Xto</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>achi bouakline mohamed</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>dfjU302n</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>mazou sacko derek</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>bokMNZhk</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t>balde ibrahima</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>bokMNZhk</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>balde ibrahima</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr">
+        <is>
+          <t>QqlDIsGM</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>bentayeb tawfik</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>pUcMCfNn</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>verdier yannis</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>pUcMCfNn</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>verdier yannis</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>p2nsMSal</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>ngouyamsa ahmad</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>rXN8qke1</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>doumbia cheick</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>rXN8qke1</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>doumbia cheick</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>QBWpvgXg</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>bouchouari mohamed</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr"/>
+      <c r="EA6" t="inlineStr"/>
+      <c r="EB6" t="inlineStr"/>
+      <c r="EC6" t="inlineStr"/>
+      <c r="ED6" t="inlineStr"/>
+      <c r="EE6" t="inlineStr"/>
+      <c r="EF6" t="inlineStr"/>
+      <c r="EG6" t="inlineStr"/>
+      <c r="EH6" t="inlineStr"/>
+      <c r="EI6" t="inlineStr"/>
+      <c r="EJ6" t="inlineStr"/>
+      <c r="EK6" t="inlineStr"/>
+      <c r="EL6" t="inlineStr"/>
+      <c r="EM6" t="inlineStr"/>
+      <c r="EN6" t="inlineStr"/>
+      <c r="EO6" t="inlineStr"/>
+      <c r="EP6" t="inlineStr">
+        <is>
+          <t>jusUrXEa</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t>skytta naatan</t>
+        </is>
+      </c>
+      <c r="ER6" t="inlineStr">
+        <is>
+          <t>jusUrXEa</t>
+        </is>
+      </c>
+      <c r="ES6" t="inlineStr">
+        <is>
+          <t>skytta naatan</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr">
+        <is>
+          <t>WSXgQK56</t>
+        </is>
+      </c>
+      <c r="EU6" t="inlineStr">
+        <is>
+          <t>bardeli enzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>UPVYr846</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EibuOrCE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>diop mamadou</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OrdAwjs0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>paquiez gaetan</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cv3T1tX1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>diarra mamadou</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>QeC1pQvn</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>tchaptchet allan</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>IXc7iymr</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>mendy arial</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0poPcske</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rigo dante</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6VcKrEuM</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>valls theo</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2NKowyxS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>sylvestre eddy</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>SzyvcCbe</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>benet jessy</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>ITex2UPE</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>kerouedan alan</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>nsRL20Ap</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>ba pape meissa</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>AXCqL4Qp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>jeannin mehdi</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>UVcaeNxh</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>gaspar jordy</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>f77lo10C</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ahoussou kouadio guy ange</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>A1JE6XmB</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>ruiz jean</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>xUaIYbZa</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>koudou therence</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>ImnpF5je</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>beusnard steeve</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>K0sjhCJO</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>mohamed iyad</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>CrYHlkps</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>mboup pathe</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>GjoN5Ete</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>mille antoine</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Ollmu17h</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>njoh yonis</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>ManhCoID</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>arconte tairyk</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>tpbpYRt1</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>allain bobby</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>QBRg7SrJ</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>bangre mamady</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>4vlM6XrP</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>elphege nesta</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0K8CfONM</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>joseph lenny</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>KE7PDGER</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>mbemba nolan</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>rqvBoQyG</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>mouyokolo loris</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>hKS4A5nd</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>zahui nesta</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>nHFb8AML</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>diawara kandet</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>ERwj7fzC</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>evans jean</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>bqTyyFdl</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>gasnier kyllian</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>EZQeQxef</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>kalulu joseph</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>EJuazaLT</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>kante ousmane</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>vyNtJpK2</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>kouassi xavier</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>0ID2g08S</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>paradowski tao</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>KE7PDGER</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>mbemba nolan</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>KE7PDGER</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>mbemba nolan</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>2NKowyxS</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>sylvestre eddy</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>0K8CfONM</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>joseph lenny</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>0K8CfONM</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>joseph lenny</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>0poPcske</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>rigo dante</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>QBRg7SrJ</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>bangre mamady</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>QBRg7SrJ</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>bangre mamady</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>ITex2UPE</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>kerouedan alan</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>hKS4A5nd</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>zahui nesta</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>hKS4A5nd</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>zahui nesta</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>SzyvcCbe</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>benet jessy</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>nHFb8AML</t>
+        </is>
+      </c>
+      <c r="DC7" t="inlineStr">
+        <is>
+          <t>diawara kandet</t>
+        </is>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>nHFb8AML</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>diawara kandet</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>Ollmu17h</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>njoh yonis</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>vyNtJpK2</t>
+        </is>
+      </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t>kouassi xavier</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>vyNtJpK2</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>kouassi xavier</t>
+        </is>
+      </c>
+      <c r="DL7" t="inlineStr">
+        <is>
+          <t>ImnpF5je</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>beusnard steeve</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>bqTyyFdl</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>gasnier kyllian</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>bqTyyFdl</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>gasnier kyllian</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>GjoN5Ete</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>mille antoine</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr"/>
+      <c r="DU7" t="inlineStr"/>
+      <c r="DV7" t="inlineStr"/>
+      <c r="DW7" t="inlineStr"/>
+      <c r="DX7" t="inlineStr"/>
+      <c r="DY7" t="inlineStr"/>
+      <c r="DZ7" t="inlineStr"/>
+      <c r="EA7" t="inlineStr"/>
+      <c r="EB7" t="inlineStr"/>
+      <c r="EC7" t="inlineStr"/>
+      <c r="ED7" t="inlineStr"/>
+      <c r="EE7" t="inlineStr"/>
+      <c r="EF7" t="inlineStr"/>
+      <c r="EG7" t="inlineStr"/>
+      <c r="EH7" t="inlineStr"/>
+      <c r="EI7" t="inlineStr"/>
+      <c r="EJ7" t="inlineStr"/>
+      <c r="EK7" t="inlineStr"/>
+      <c r="EL7" t="inlineStr"/>
+      <c r="EM7" t="inlineStr"/>
+      <c r="EN7" t="inlineStr"/>
+      <c r="EO7" t="inlineStr"/>
+      <c r="EP7" t="inlineStr"/>
+      <c r="EQ7" t="inlineStr"/>
+      <c r="ER7" t="inlineStr"/>
+      <c r="ES7" t="inlineStr"/>
+      <c r="ET7" t="inlineStr"/>
+      <c r="EU7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8WI0c7Ja</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A9ux8Ef8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>basilio enzo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4tt9cPfg</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sissoko alpha</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KAGBPuyQ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nair sohaib</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>fsOSS7y0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>riou mathis</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>McCSZuxs</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>sagna amadou</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>pC1OCXV4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>louiserre dylan</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>29krq31i</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>sidibe kalidou</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>QPweXact</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>vallier lenny</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>27PxWKIj</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>hemia amine</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>GxfU6qGd</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>picard hugo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>GxWPthlH</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>siwe jacques</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>dl7hEyx3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>beunardeau quentin</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>bD4oBeZu</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>danger bradlay</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>WEf5zAtn</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>mendy bissenty</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>CjerQdJC</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>kouagba loic</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>bDfdmD9h</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>doucoure fode</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>l0CB1r2R</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>dembi fred</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>xbSVpTij</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>renel samuel</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Cf8ju4GK</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>hachem ryad</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>lUS5czaO</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>ifnaoui merwan</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>tYd2ZZ4l</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>durand damien</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>G4gI1g5M</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>badji aliou</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>Yw1VmcL6</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>gomis donacien</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>zH8Wrlde</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>labeau brighton</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>WYiQmqg2</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>luvambo taylor</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>8IfBwmXp</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>maronnier lucas</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0dlneXN6</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>mendes junior armando</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>EFZ6icqq</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>mbaye babacar</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>t8ya9KXl</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>touzghar rayan</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>xATlu4A5</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>benali hacene</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>EeeUoqnD</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>bonet pepe</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>Eqg3ERA3</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>botella ivann</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>j3IsAvo7</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>cisse kemo</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>0dlneXN6</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>mendes junior armando</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>0dlneXN6</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>mendes junior armando</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>McCSZuxs</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>sagna amadou</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>WYiQmqg2</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>luvambo taylor</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>WYiQmqg2</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>luvambo taylor</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>29krq31i</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>sidibe kalidou</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>zH8Wrlde</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>labeau brighton</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>zH8Wrlde</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>labeau brighton</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>GxfU6qGd</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>picard hugo</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>8IfBwmXp</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>maronnier lucas</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>8IfBwmXp</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>maronnier lucas</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>QPweXact</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>vallier lenny</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>xATlu4A5</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>benali hacene</t>
+        </is>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>xATlu4A5</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>benali hacene</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>G4gI1g5M</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>badji aliou</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="DI8" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>M13pWJRa</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>durivaux dylan</t>
+        </is>
+      </c>
+      <c r="DL8" t="inlineStr">
+        <is>
+          <t>bDfdmD9h</t>
+        </is>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>doucoure fode</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>KhMVtudH</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
+          <t>el hriti aniss</t>
+        </is>
+      </c>
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>Cf8ju4GK</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>hachem ryad</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>GpETZfpE</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>escartin josue</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
         <is>
           <t>l0CB1r2R</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="DY8" t="inlineStr">
         <is>
           <t>dembi fred</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>zkh2UjHb</t>
-        </is>
-      </c>
-      <c r="CI3" t="inlineStr">
-        <is>
-          <t>eickmayer joachim</t>
-        </is>
-      </c>
-      <c r="CJ3" t="inlineStr">
-        <is>
-          <t>G4gI1g5M</t>
-        </is>
-      </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>badji aliou</t>
-        </is>
-      </c>
-      <c r="CL3" t="inlineStr">
-        <is>
-          <t>G4gI1g5M</t>
-        </is>
-      </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>badji aliou</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>tYd2ZZ4l</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>durand damien</t>
-        </is>
-      </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>MT98e48G</t>
-        </is>
-      </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>jabol folcarelli tim</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>MT98e48G</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>jabol folcarelli tim</t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>vXAsoH78</t>
-        </is>
-      </c>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>puch herrantz mehdi</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>ptT4ile8</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>toure al hassan</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>ptT4ile8</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>toure al hassan</t>
-        </is>
-      </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>xtTKOiHO</t>
-        </is>
-      </c>
-      <c r="DA3" t="inlineStr">
-        <is>
-          <t>jacob valentin</t>
-        </is>
-      </c>
-      <c r="DB3" t="inlineStr">
-        <is>
-          <t>CtZ04TjI</t>
-        </is>
-      </c>
-      <c r="DC3" t="inlineStr">
-        <is>
-          <t>soumano moussa</t>
-        </is>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>CtZ04TjI</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>soumano moussa</t>
-        </is>
-      </c>
-      <c r="DF3" t="inlineStr">
-        <is>
-          <t>GfQuApsR</t>
-        </is>
-      </c>
-      <c r="DG3" t="inlineStr">
-        <is>
-          <t>ibayi christopher</t>
-        </is>
-      </c>
-      <c r="DH3" t="inlineStr">
-        <is>
-          <t>dfsrq39I</t>
-        </is>
-      </c>
-      <c r="DI3" t="inlineStr">
-        <is>
-          <t>vidal clement</t>
-        </is>
-      </c>
-      <c r="DJ3" t="inlineStr">
-        <is>
-          <t>dfsrq39I</t>
-        </is>
-      </c>
-      <c r="DK3" t="inlineStr">
-        <is>
-          <t>vidal clement</t>
-        </is>
-      </c>
-      <c r="DL3" t="inlineStr">
-        <is>
-          <t>tWEjLiqi</t>
-        </is>
-      </c>
-      <c r="DM3" t="inlineStr">
-        <is>
-          <t>bamba axel</t>
-        </is>
-      </c>
-      <c r="DN3" t="inlineStr"/>
-      <c r="DO3" t="inlineStr"/>
-      <c r="DP3" t="inlineStr"/>
-      <c r="DQ3" t="inlineStr"/>
-      <c r="DR3" t="inlineStr"/>
-      <c r="DS3" t="inlineStr"/>
-      <c r="DT3" t="inlineStr"/>
-      <c r="DU3" t="inlineStr"/>
-      <c r="DV3" t="inlineStr"/>
-      <c r="DW3" t="inlineStr"/>
-      <c r="DX3" t="inlineStr">
-        <is>
-          <t>M13pWJRa</t>
-        </is>
-      </c>
-      <c r="DY3" t="inlineStr">
-        <is>
-          <t>durivaux dylan</t>
-        </is>
-      </c>
-      <c r="DZ3" t="inlineStr">
-        <is>
-          <t>M13pWJRa</t>
-        </is>
-      </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>durivaux dylan</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
-        <is>
-          <t>bDfdmD9h</t>
-        </is>
-      </c>
-      <c r="EC3" t="inlineStr">
-        <is>
-          <t>doucoure fode</t>
-        </is>
-      </c>
-      <c r="ED3" t="inlineStr">
-        <is>
-          <t>KhMVtudH</t>
-        </is>
-      </c>
-      <c r="EE3" t="inlineStr">
-        <is>
-          <t>el hriti aniss</t>
-        </is>
-      </c>
-      <c r="EF3" t="inlineStr">
-        <is>
-          <t>KhMVtudH</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
-        <is>
-          <t>el hriti aniss</t>
-        </is>
-      </c>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>xbSVpTij</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr">
-        <is>
-          <t>renel samuel</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr">
-        <is>
-          <t>GpETZfpE</t>
-        </is>
-      </c>
-      <c r="EK3" t="inlineStr">
-        <is>
-          <t>escartin josue</t>
-        </is>
-      </c>
-      <c r="EL3" t="inlineStr">
-        <is>
-          <t>GpETZfpE</t>
-        </is>
-      </c>
-      <c r="EM3" t="inlineStr">
-        <is>
-          <t>escartin josue</t>
-        </is>
-      </c>
-      <c r="EN3" t="inlineStr">
-        <is>
-          <t>WEf5zAtn</t>
-        </is>
-      </c>
-      <c r="EO3" t="inlineStr">
-        <is>
-          <t>mendy bissenty</t>
-        </is>
-      </c>
-      <c r="EP3" t="inlineStr">
-        <is>
-          <t>lMOq4ljm</t>
-        </is>
-      </c>
-      <c r="EQ3" t="inlineStr">
-        <is>
-          <t>mangani thomas</t>
-        </is>
-      </c>
-      <c r="ER3" t="inlineStr">
-        <is>
-          <t>lMOq4ljm</t>
-        </is>
-      </c>
-      <c r="ES3" t="inlineStr">
-        <is>
-          <t>mangani thomas</t>
-        </is>
-      </c>
-      <c r="ET3" t="inlineStr">
-        <is>
-          <t>4Ug33NLF</t>
-        </is>
-      </c>
-      <c r="EU3" t="inlineStr">
-        <is>
-          <t>anziani julien</t>
-        </is>
-      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>j3IsAvo7</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>cisse kemo</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>j3IsAvo7</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>cisse kemo</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>lUS5czaO</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>ifnaoui merwan</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr"/>
+      <c r="EG8" t="inlineStr"/>
+      <c r="EH8" t="inlineStr"/>
+      <c r="EI8" t="inlineStr"/>
+      <c r="EJ8" t="inlineStr"/>
+      <c r="EK8" t="inlineStr"/>
+      <c r="EL8" t="inlineStr"/>
+      <c r="EM8" t="inlineStr"/>
+      <c r="EN8" t="inlineStr"/>
+      <c r="EO8" t="inlineStr"/>
+      <c r="EP8" t="inlineStr"/>
+      <c r="EQ8" t="inlineStr"/>
+      <c r="ER8" t="inlineStr"/>
+      <c r="ES8" t="inlineStr"/>
+      <c r="ET8" t="inlineStr"/>
+      <c r="EU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QiPssnZI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GvRRSA15</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>aymes jeremy</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CI9LnrCi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>saintini nathanael</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>bw41ww90</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>morante leandro</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>K6gqRt3c</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>falette simon</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>zciOF0Jn</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>amraoui ayoub</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>drXPszOh</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>solvet steve</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>AuRgvOVQ</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>robin milan</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>8GM9rzEp</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>belloumou samir</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>KAGdlKQ8</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>bamba mohamed</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>xA5oIAIk</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>ipiele alain</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>jFzgBj16</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>ouotro patrick</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>hz9iLSns</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>placide johnny</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>dGEFacR1</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>bohnert florian</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>SGS1GzV5</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>akueson gustave</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>IwWAp1LB</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>guevara juan</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>tIMjIu1I</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>ariss zakaria</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>EodMM41U</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>vincent christophe</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ronEz0Iq</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>ducrocq tom</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>b9dIWhMU</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>onana cyrille</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0f89SvvA</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>tramoni lisandru</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>xr3SdJz4</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>rodrigues clement</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>vVf0mSM7</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>boutrah amine</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>fuqL2LJ2</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>bonalair max</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>6c3rD50k</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>djaha akim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>GM3MZsvr</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>etile yannick</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>Yye7kYuP</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>gautier luan</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>QgF8WB2F</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>kembolo francis</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0MPqros3</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>mendy oucasse</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>fTP84ZUd</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>shamal steve</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>vcfrwUSo</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>boumaaoui mohamed amine</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>4Ou8BC7i</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>cisse lamine</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>OdiG9Lyg</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>fabri julien</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>KK953yrm</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>inao oulai christ</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>S8afnvrC</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>maggiotti julien</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>4C2mjUxk</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>roncaglia anthony</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>x6p5H6p3</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>tavares dylan</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>hKSaXL8F</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>zouaoui ilyes</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>8GM9rzEp</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>belloumou samir</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>fTP84ZUd</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>shamal steve</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>fTP84ZUd</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>shamal steve</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>jFzgBj16</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>ouotro patrick</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>0MPqros3</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>mendy oucasse</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>0MPqros3</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>mendy oucasse</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>xA5oIAIk</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>ipiele alain</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>4Ou8BC7i</t>
+        </is>
+      </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>cisse lamine</t>
+        </is>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>4Ou8BC7i</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>cisse lamine</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>0f89SvvA</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>tramoni lisandru</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>S8afnvrC</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>maggiotti julien</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>S8afnvrC</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>maggiotti julien</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>EodMM41U</t>
+        </is>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>vincent christophe</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>vcfrwUSo</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>boumaaoui mohamed amine</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>vcfrwUSo</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>boumaaoui mohamed amine</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>xr3SdJz4</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>rodrigues clement</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>x6p5H6p3</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>tavares dylan</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>x6p5H6p3</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>tavares dylan</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>vVf0mSM7</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>boutrah amine</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr"/>
+      <c r="EA9" t="inlineStr"/>
+      <c r="EB9" t="inlineStr"/>
+      <c r="EC9" t="inlineStr"/>
+      <c r="ED9" t="inlineStr"/>
+      <c r="EE9" t="inlineStr"/>
+      <c r="EF9" t="inlineStr"/>
+      <c r="EG9" t="inlineStr"/>
+      <c r="EH9" t="inlineStr"/>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
+      <c r="EK9" t="inlineStr"/>
+      <c r="EL9" t="inlineStr"/>
+      <c r="EM9" t="inlineStr"/>
+      <c r="EN9" t="inlineStr"/>
+      <c r="EO9" t="inlineStr"/>
+      <c r="EP9" t="inlineStr"/>
+      <c r="EQ9" t="inlineStr"/>
+      <c r="ER9" t="inlineStr"/>
+      <c r="ES9" t="inlineStr"/>
+      <c r="ET9" t="inlineStr"/>
+      <c r="EU9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG5"/>
+  <dimension ref="A1:FE7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -951,2303 +951,2377 @@
       </c>
       <c r="DB1" s="1" t="inlineStr">
         <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
           <t>id_player_sub_enter_away_1</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_1</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_2</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_2</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_3</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_3</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_4</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_4</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_5</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_5</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_6</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_6</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_7</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_7</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_8</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_8</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_9</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_9</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_10</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_10</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_11</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_11</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_12</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_12</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_13</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_13</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_14</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_14</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>id_player_sub_enter_away_15</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>player_name_sub_enter_away_15</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_1</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_1</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_2</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_2</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_3</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_3</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_4</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_4</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_5</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_5</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_5</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_13</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_14</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_home_15</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_home_15</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qe5HfcWe</t>
+          <t>IsTiBa8d</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lecomte benjamin</t>
+          <t>chevalier lucas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WOiB5ygg</t>
+          <t>YeGIfsnH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>sacko falaye</t>
+          <t>diakite bafode</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>hQGrDm2I</t>
+          <t>0hxFjbCm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>omeragic becir</t>
+          <t>mandi aissa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>pYI2rM4H</t>
+          <t>6kFjexWI</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>sagnan modibo</t>
+          <t>alexsandro</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IFhobcS1</t>
+          <t>vBypn8GA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>sylla issiaga</t>
+          <t>santos tiago</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>bkWk025d</t>
+          <t>YPYwQXje</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>chotard joris</t>
+          <t>andre benjamin</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>j5dSkdZI</t>
+          <t>AmAtkgFg</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>ferri jordan</t>
+          <t>gomes angel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Y7pbUJA4</t>
+          <t>0zzTdK1T</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>al tamari mousa suleiman</t>
+          <t>gudmundsson gabriel</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>vsv6TioJ</t>
+          <t>vqK5oQ8e</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>savanier teji</t>
+          <t>zhegrova edon</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2qMy8CA5</t>
+          <t>UZDgIuNN</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>coulibaly tanguy</t>
+          <t>haraldsson hakon arnar</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>nks9eiQ4</t>
+          <t>dtOEHzit</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>adams akor</t>
+          <t>bayo mohamed</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>p64JKtYL</t>
+          <t>WScbdXmL</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>lafont alban</t>
+          <t>donnarumma gianluigi</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>vLPNfRe2</t>
+          <t>MqFBkBsp</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>coco marcus</t>
+          <t>hakimi achraf</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2XnIOLsp</t>
+          <t>UFfev8HP</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>pallois nicolas</t>
+          <t>marquinhos</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>xYHsz2uS</t>
+          <t>KA5AQsy0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>zeze nathan</t>
+          <t>pacho william</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>G6Icx4DR</t>
+          <t>Y1UU1rz7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>duverne jean kevin</t>
+          <t>lucas beraldo</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2NKKC5LI</t>
+          <t>hCbYVsXQ</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>chirivella pedro</t>
+          <t>neves joao</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>21Ny44li</t>
+          <t>neJeseDL</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>lepenant johann</t>
+          <t>zaire emery warren</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>YHDXXra7</t>
+          <t>Sz9SH7zj</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>thomas sorba</t>
+          <t>vitinha</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0vxfG1Jf</t>
+          <t>zsMC2Ec0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>kadewere tino</t>
+          <t>dembele ousmane</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Cj5rnjpG</t>
+          <t>GQMMQo6m</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>simon moses</t>
+          <t>asensio marco</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>4pCFSl1P</t>
+          <t>lhGD3RgS</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>abline matthis</t>
+          <t>barcola bradley</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>GUpH52h6</t>
+          <t>dpoNasPg</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>bares gabriel</t>
+          <t>bouaddi ayyoub</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>GKgj13Ht</t>
+          <t>hl6k3P1f</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>bertaud dimitry</t>
+          <t>cabella remy</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>dYGOQd5o</t>
+          <t>hjUt2GRb</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>chennahi theo</t>
+          <t>caillard marc aurele</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>S4sVF7O0</t>
+          <t>CSvtXj2E</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>dzodic stefan</t>
+          <t>david jonathan</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>Qwp5yt4r</t>
+          <t>0vPhfqq8</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>fayad khalil</t>
+          <t>fernandez pardo mathias</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>pA3wMl0B</t>
+          <t>WUyrShAL</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>issoufou yanis ali</t>
+          <t>meunier thomas</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>Q7VDuZr1</t>
+          <t>2Nyle1h2</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>khazri wahbi</t>
+          <t>mukau ngal ayel</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>A1rzEd2O</t>
+          <t>KjBOZTeI</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>inzingoula rabby</t>
+          <t>sahraoui osame</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>QHKswk6H</t>
+          <t>0l0PGXES</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>tchato enzo</t>
+          <t>toure ousmane</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>Qm7z6ES9</t>
+          <t>KIUWH2Jq</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>acapandie mathieu</t>
+          <t>doue desire</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>M7BOiYYH</t>
+          <t>WKBRZ6Y6</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>amian adou kelvin</t>
+          <t>kolo muani randal</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>UHFZg7zc</t>
+          <t>YTVIJfxO</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>assoumani dehmaine</t>
+          <t>lee kangin</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>AsPIAoni</t>
+          <t>za4zLeYc</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>augusto douglas</t>
+          <t>mayulu senny</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>xK337SFG</t>
+          <t>nkxtcGo7</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>barbet hugo</t>
+          <t>mbaye ibrahim</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>2BI6b6Qj</t>
+          <t>l6HSH2Uo</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>cozza nicolas</t>
+          <t>ruiz fabian</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>AiotaxUt</t>
+          <t>EqBuG0nE</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>guirassy bahereba</t>
+          <t>skriniar milan</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>zy2QKhzd</t>
+          <t>CnNoZhXr</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>leroux louis</t>
+          <t>tenas arnau</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>roG6AGUf</t>
+          <t>S2Gd6Dq5</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>mostafa mohamed</t>
+          <t>zague yoram</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>QHKswk6H</t>
+          <t>KjBOZTeI</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>tchato enzo</t>
+          <t>sahraoui osame</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>QHKswk6H</t>
+          <t>KjBOZTeI</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>tchato enzo</t>
+          <t>sahraoui osame</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>IFhobcS1</t>
+          <t>UZDgIuNN</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>sylla issiaga</t>
+          <t>haraldsson hakon arnar</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>A1rzEd2O</t>
+          <t>2Nyle1h2</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>inzingoula rabby</t>
+          <t>mukau ngal ayel</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>A1rzEd2O</t>
+          <t>2Nyle1h2</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>inzingoula rabby</t>
+          <t>mukau ngal ayel</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>bkWk025d</t>
+          <t>AmAtkgFg</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>chotard joris</t>
+          <t>gomes angel</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>Qwp5yt4r</t>
+          <t>WUyrShAL</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>fayad khalil</t>
+          <t>meunier thomas</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>Qwp5yt4r</t>
+          <t>WUyrShAL</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>fayad khalil</t>
+          <t>meunier thomas</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>Y7pbUJA4</t>
+          <t>0hxFjbCm</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>al tamari mousa suleiman</t>
+          <t>mandi aissa</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>Q7VDuZr1</t>
+          <t>CSvtXj2E</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>khazri wahbi</t>
+          <t>david jonathan</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>Q7VDuZr1</t>
+          <t>CSvtXj2E</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>khazri wahbi</t>
+          <t>david jonathan</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>2qMy8CA5</t>
+          <t>dtOEHzit</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>coulibaly tanguy</t>
+          <t>bayo mohamed</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>M7BOiYYH</t>
+          <t>hl6k3P1f</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>amian adou kelvin</t>
+          <t>cabella remy</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>M7BOiYYH</t>
+          <t>hl6k3P1f</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>amian adou kelvin</t>
+          <t>cabella remy</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>YHDXXra7</t>
+          <t>vBypn8GA</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>thomas sorba</t>
+          <t>santos tiago</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>roG6AGUf</t>
+          <t>KIUWH2Jq</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>mostafa mohamed</t>
+          <t>doue desire</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>roG6AGUf</t>
+          <t>KIUWH2Jq</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>mostafa mohamed</t>
+          <t>doue desire</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>4pCFSl1P</t>
+          <t>GQMMQo6m</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>abline matthis</t>
+          <t>asensio marco</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>zy2QKhzd</t>
+          <t>l6HSH2Uo</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>leroux louis</t>
+          <t>ruiz fabian</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>zy2QKhzd</t>
+          <t>l6HSH2Uo</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>leroux louis</t>
+          <t>ruiz fabian</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>vLPNfRe2</t>
+          <t>hCbYVsXQ</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>coco marcus</t>
+          <t>neves joao</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>AiotaxUt</t>
+          <t>YTVIJfxO</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>guirassy bahereba</t>
+          <t>lee kangin</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>AiotaxUt</t>
+          <t>YTVIJfxO</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>guirassy bahereba</t>
+          <t>lee kangin</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>Cj5rnjpG</t>
+          <t>lhGD3RgS</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>simon moses</t>
+          <t>barcola bradley</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>2BI6b6Qj</t>
+          <t>WKBRZ6Y6</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>cozza nicolas</t>
+          <t>kolo muani randal</t>
         </is>
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>2BI6b6Qj</t>
+          <t>WKBRZ6Y6</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>cozza nicolas</t>
+          <t>kolo muani randal</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>0vxfG1Jf</t>
+          <t>zsMC2Ec0</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>kadewere tino</t>
+          <t>dembele ousmane</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>dSDrHenE</t>
+          <t>za4zLeYc</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>gueguin axel</t>
+          <t>mayulu senny</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>4hOup61a</t>
+          <t>za4zLeYc</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>jullien christopher</t>
+          <t>mayulu senny</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>ERFuKxAR</t>
+          <t>MqFBkBsp</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>kouyate boubakar</t>
+          <t>hakimi achraf</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
         <is>
-          <t>AX8IYJcC</t>
+          <t>zB5OlUKE</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>mincarelli lucas</t>
+          <t>bakker mitchel</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>A7vSQTKq</t>
+          <t>UVRm5Kjk</t>
         </is>
       </c>
       <c r="EO2" t="inlineStr">
         <is>
-          <t>nordin arnaud</t>
+          <t>bentaleb nabil</t>
         </is>
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t>G8o32H2s</t>
+          <t>neNU9A9F</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>sainte luce theo</t>
+          <t>ismaily</t>
         </is>
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t>MiH8I5Na</t>
+          <t>zsH7aMfI</t>
         </is>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
-          <t>castelletto jean charles</t>
+          <t>umtiti samuel</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t>hYtVzJ13</t>
+          <t>xGol69CN</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
         <is>
-          <t>centonze fabien</t>
+          <t>zedadka akim</t>
         </is>
       </c>
       <c r="EV2" t="inlineStr">
         <is>
-          <t>GCkY7Wy8</t>
+          <t>x2fvnkud</t>
         </is>
       </c>
       <c r="EW2" t="inlineStr">
         <is>
-          <t>ganago igniatius</t>
+          <t>hernandez lucas</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t>l2t9fvR7</t>
+          <t>dMyiR1D8</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
         <is>
-          <t>mahamoud adel</t>
+          <t>kimpembe presnel</t>
         </is>
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t>0t5Mjaa6</t>
+          <t>ne2xCTJj</t>
         </is>
       </c>
       <c r="FA2" t="inlineStr">
         <is>
-          <t>mollet florent</t>
-        </is>
-      </c>
-      <c r="FB2" t="inlineStr"/>
-      <c r="FC2" t="inlineStr"/>
-      <c r="FD2" t="inlineStr"/>
-      <c r="FE2" t="inlineStr"/>
-      <c r="FF2" t="inlineStr"/>
-      <c r="FG2" t="inlineStr"/>
+          <t>mendes nuno</t>
+        </is>
+      </c>
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t>xfW2M1Tt</t>
+        </is>
+      </c>
+      <c r="FC2" t="inlineStr">
+        <is>
+          <t>ramos goncalo</t>
+        </is>
+      </c>
+      <c r="FD2" t="inlineStr">
+        <is>
+          <t>zJF3W9Rq</t>
+        </is>
+      </c>
+      <c r="FE2" t="inlineStr">
+        <is>
+          <t>safonov matvey</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OlUQhqqo</t>
+          <t>rqDavwpd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bizot marco</t>
+          <t>fofana yahia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0IiimISF</t>
+          <t>lvXo8mgi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>lala kenny</t>
+          <t>carlens arcus</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GnvxP2X3</t>
+          <t>ngxkIxtK</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>chardonnet brendan</t>
+          <t>bamba abdoulaye</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>hEHAtkEC</t>
+          <t>dpU7jLLp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>le cardinal julien</t>
+          <t>hountondji cedric</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>xQENPIHR</t>
+          <t>ADepyvio</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>amavi jordan</t>
+          <t>lefort jordan</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>IsJ0zlTM</t>
+          <t>f9CImc7o</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>camara mahdi</t>
+          <t>ekomie jacques</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>YJ2AR519</t>
+          <t>xbHA9hT8</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>magnetti hugo</t>
+          <t>aholou jean eudes</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>h8g5dFkH</t>
+          <t>4ErwI0V0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>faivre romain</t>
+          <t>belkhdim yassine</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>hnER3xyT</t>
+          <t>tIm0BT62</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>del castillo romain</t>
+          <t>abdelli himad</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>MPlU0iTh</t>
+          <t>Yu4ZEgGr</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>ajorque ludovic</t>
+          <t>el melali farid</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>xzssoNnp</t>
+          <t>tSVHHLjn</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>sima abdallah</t>
+          <t>cherif sidiki</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>IH9cf1NH</t>
+          <t>633bsauA</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>larsonneur gautier</t>
+          <t>bulka marcin</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>by5QHeY8</t>
+          <t>6acylKhj</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>macon yvann</t>
+          <t>ndayishimiye youssouf</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>QcLd3bL1</t>
+          <t>4dBTEEF3</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>batubinsika dylan</t>
+          <t>bombito moise</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>OYtRcGFm</t>
+          <t>nNPcDNFr</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>abdelhamid yunis</t>
+          <t>dante</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>67mIaVqd</t>
+          <t>Ag37eHIn</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>cornud pierre</t>
+          <t>clauss jonathan</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0SDVC1gR</t>
+          <t>URcBI8WC</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>fomba lamine</t>
+          <t>boudaoui hichem</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>W6Xd8Gyg</t>
+          <t>GEIWE1pD</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>amougou mathis</t>
+          <t>ndombele tanguy</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>W6PE7nsb</t>
+          <t>Q1kigul6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>aiki ayman</t>
+          <t>bard melvin</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>fkTUaOi8</t>
+          <t>xOd4FVMQ</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>davitashvili zuriko</t>
+          <t>cho mohamed ali</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>dKzjZfiI</t>
+          <t>QXyb0B8i</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>cafaro mathieu</t>
+          <t>guessand evann</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>MDGbgDq7</t>
+          <t>6V4D771e</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>sissoko ibrahim</t>
+          <t>bouanani badredine</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>OnmmDvKS</t>
+          <t>rgmBFVFk</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>camblan axel</t>
+          <t>biumla emmanuel</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>zHCAxaZn</t>
+          <t>zshOz5Bl</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>coudert gregoire</t>
+          <t>capelle pierrick</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>YLVl99Q1</t>
+          <t>ba2ejA41</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>coulibaly soumaila</t>
+          <t>dieng bamba cheikh dieng</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>xbRv7JLU</t>
+          <t>hA8XZuUp</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>diop serigne</t>
+          <t>ferhat zinedine</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>pniy3Ny3</t>
+          <t>GAXAKdkE</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>kante ibrahim</t>
+          <t>hanin florent</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>tQMgOwhG</t>
+          <t>GGw2OEMr</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>martin jonas</t>
+          <t>lepaul esteban</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>n5sFh1Ch</t>
+          <t>Q1LRmF1l</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>pereira mathias</t>
+          <t>ould khaled zinedine</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>bmj4mkKq</t>
+          <t>dlgWt8kH</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>luc zogbe</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
+          <t>rao lisoa lilian</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>Agm4z1Gk</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>zinga melvin</t>
+        </is>
+      </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>2acUGEci</t>
+          <t>t4ZaE4G9</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>appiah dennis</t>
+          <t>abdelmoneim mohamed</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>fFRVaYCs</t>
+          <t>pEEqeFXD</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>gauthier antoine</t>
+          <t>boga jeremie</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>GGYnig7m</t>
+          <t>82MFl4r8</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>maubleu brice</t>
+          <t>boulhendi teddy</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>zRiphMYO</t>
+          <t>bgCF8FZ6</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>moueffek aimen</t>
+          <t>brahimi bilal</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>tArngh4I</t>
+          <t>lz4moDgp</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>mouton louis</t>
+          <t>dupe maxime</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>SG64s4Ks</t>
+          <t>zRrXS0P0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>nade mickael</t>
+          <t>mendy antoine</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>db3kbs2N</t>
+          <t>vZ2CcIMA</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>petrot leo</t>
+          <t>moukoko youssoufa</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>S0fUJqv9</t>
+          <t>2RTbyFaC</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>tardieu florian</t>
+          <t>orakpo victor</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>vswx9zEb</t>
+          <t>E9pRzPPA</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>wadji ibrahima</t>
+          <t>rosario pablo</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>tQMgOwhG</t>
+          <t>ba2ejA41</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>martin jonas</t>
+          <t>dieng bamba cheikh dieng</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>tQMgOwhG</t>
+          <t>ba2ejA41</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>martin jonas</t>
+          <t>dieng bamba cheikh dieng</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>xzssoNnp</t>
+          <t>lvXo8mgi</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>sima abdallah</t>
+          <t>carlens arcus</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>bmj4mkKq</t>
+          <t>GAXAKdkE</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>luc zogbe</t>
+          <t>hanin florent</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>bmj4mkKq</t>
+          <t>GAXAKdkE</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>luc zogbe</t>
+          <t>hanin florent</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>xQENPIHR</t>
+          <t>f9CImc7o</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>amavi jordan</t>
+          <t>ekomie jacques</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>YLVl99Q1</t>
+          <t>zshOz5Bl</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>coulibaly soumaila</t>
+          <t>capelle pierrick</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>YLVl99Q1</t>
+          <t>zshOz5Bl</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>coulibaly soumaila</t>
+          <t>capelle pierrick</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>hEHAtkEC</t>
+          <t>xbHA9hT8</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
         <is>
-          <t>le cardinal julien</t>
+          <t>aholou jean eudes</t>
         </is>
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>n5sFh1Ch</t>
+          <t>dlgWt8kH</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>pereira mathias</t>
+          <t>rao lisoa lilian</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>n5sFh1Ch</t>
+          <t>dlgWt8kH</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>pereira mathias</t>
+          <t>rao lisoa lilian</t>
         </is>
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>h8g5dFkH</t>
+          <t>ngxkIxtK</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>faivre romain</t>
+          <t>bamba abdoulaye</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>2acUGEci</t>
+          <t>hA8XZuUp</t>
         </is>
       </c>
       <c r="DC3" t="inlineStr">
         <is>
-          <t>appiah dennis</t>
+          <t>ferhat zinedine</t>
         </is>
       </c>
       <c r="DD3" t="inlineStr">
         <is>
-          <t>2acUGEci</t>
+          <t>hA8XZuUp</t>
         </is>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>appiah dennis</t>
+          <t>ferhat zinedine</t>
         </is>
       </c>
       <c r="DF3" t="inlineStr">
         <is>
-          <t>by5QHeY8</t>
+          <t>4ErwI0V0</t>
         </is>
       </c>
       <c r="DG3" t="inlineStr">
         <is>
-          <t>macon yvann</t>
+          <t>belkhdim yassine</t>
         </is>
       </c>
       <c r="DH3" t="inlineStr">
         <is>
-          <t>vswx9zEb</t>
+          <t>pEEqeFXD</t>
         </is>
       </c>
       <c r="DI3" t="inlineStr">
         <is>
-          <t>wadji ibrahima</t>
+          <t>boga jeremie</t>
         </is>
       </c>
       <c r="DJ3" t="inlineStr">
         <is>
-          <t>vswx9zEb</t>
+          <t>pEEqeFXD</t>
         </is>
       </c>
       <c r="DK3" t="inlineStr">
         <is>
-          <t>wadji ibrahima</t>
+          <t>boga jeremie</t>
         </is>
       </c>
       <c r="DL3" t="inlineStr">
         <is>
-          <t>W6PE7nsb</t>
+          <t>6V4D771e</t>
         </is>
       </c>
       <c r="DM3" t="inlineStr">
         <is>
-          <t>aiki ayman</t>
+          <t>bouanani badredine</t>
         </is>
       </c>
       <c r="DN3" t="inlineStr">
         <is>
-          <t>zRiphMYO</t>
+          <t>zRrXS0P0</t>
         </is>
       </c>
       <c r="DO3" t="inlineStr">
         <is>
-          <t>moueffek aimen</t>
+          <t>mendy antoine</t>
         </is>
       </c>
       <c r="DP3" t="inlineStr">
         <is>
-          <t>zRiphMYO</t>
+          <t>zRrXS0P0</t>
         </is>
       </c>
       <c r="DQ3" t="inlineStr">
         <is>
-          <t>moueffek aimen</t>
+          <t>mendy antoine</t>
         </is>
       </c>
       <c r="DR3" t="inlineStr">
         <is>
-          <t>0SDVC1gR</t>
+          <t>Ag37eHIn</t>
         </is>
       </c>
       <c r="DS3" t="inlineStr">
         <is>
-          <t>fomba lamine</t>
+          <t>clauss jonathan</t>
         </is>
       </c>
       <c r="DT3" t="inlineStr">
         <is>
-          <t>db3kbs2N</t>
+          <t>t4ZaE4G9</t>
         </is>
       </c>
       <c r="DU3" t="inlineStr">
         <is>
-          <t>petrot leo</t>
+          <t>abdelmoneim mohamed</t>
         </is>
       </c>
       <c r="DV3" t="inlineStr">
         <is>
-          <t>db3kbs2N</t>
+          <t>t4ZaE4G9</t>
         </is>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>petrot leo</t>
+          <t>abdelmoneim mohamed</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>67mIaVqd</t>
+          <t>xOd4FVMQ</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>cornud pierre</t>
+          <t>cho mohamed ali</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>S0fUJqv9</t>
+          <t>2RTbyFaC</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>tardieu florian</t>
+          <t>orakpo victor</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>S0fUJqv9</t>
+          <t>2RTbyFaC</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>tardieu florian</t>
+          <t>orakpo victor</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>W6Xd8Gyg</t>
+          <t>QXyb0B8i</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>amougou mathis</t>
+          <t>guessand evann</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>pQ5GqXFF</t>
+          <t>E9pRzPPA</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>locko bradley</t>
+          <t>rosario pablo</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>jgQdIv76</t>
+          <t>E9pRzPPA</t>
         </is>
       </c>
       <c r="EI3" t="inlineStr">
         <is>
-          <t>n diaye niakhate</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr"/>
-      <c r="EK3" t="inlineStr"/>
-      <c r="EL3" t="inlineStr"/>
-      <c r="EM3" t="inlineStr"/>
-      <c r="EN3" t="inlineStr"/>
-      <c r="EO3" t="inlineStr"/>
-      <c r="EP3" t="inlineStr"/>
-      <c r="EQ3" t="inlineStr"/>
-      <c r="ER3" t="inlineStr">
-        <is>
-          <t>2kCSVLV8</t>
-        </is>
-      </c>
-      <c r="ES3" t="inlineStr">
-        <is>
-          <t>bentayg mahmoud</t>
-        </is>
-      </c>
-      <c r="ET3" t="inlineStr">
-        <is>
-          <t>KKGaeL7f</t>
-        </is>
-      </c>
-      <c r="EU3" t="inlineStr">
-        <is>
-          <t>briancon anthony</t>
-        </is>
-      </c>
-      <c r="EV3" t="inlineStr"/>
-      <c r="EW3" t="inlineStr"/>
-      <c r="EX3" t="inlineStr"/>
-      <c r="EY3" t="inlineStr"/>
-      <c r="EZ3" t="inlineStr"/>
-      <c r="FA3" t="inlineStr"/>
+          <t>rosario pablo</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>GEIWE1pD</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>ndombele tanguy</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>QiEHuYPM</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>allevinah jim</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>WdtzR8gp</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>kalumba justin noel</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>SdIAUhSt</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>lopy joseph</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr"/>
+      <c r="ES3" t="inlineStr"/>
+      <c r="ET3" t="inlineStr"/>
+      <c r="EU3" t="inlineStr"/>
+      <c r="EV3" t="inlineStr">
+        <is>
+          <t>8fA5XmQC</t>
+        </is>
+      </c>
+      <c r="EW3" t="inlineStr">
+        <is>
+          <t>diop sofiane</t>
+        </is>
+      </c>
+      <c r="EX3" t="inlineStr">
+        <is>
+          <t>KdLy7rKC</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
+          <t>laborde gaetan</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
+          <t>neBI4fSj</t>
+        </is>
+      </c>
+      <c r="FA3" t="inlineStr">
+        <is>
+          <t>louchet tom</t>
+        </is>
+      </c>
       <c r="FB3" t="inlineStr">
         <is>
-          <t>OnmmDvKS</t>
+          <t>ny2HpVKp</t>
         </is>
       </c>
       <c r="FC3" t="inlineStr">
         <is>
-          <t>camblan axel</t>
+          <t>moffi teremas</t>
         </is>
       </c>
       <c r="FD3" t="inlineStr">
         <is>
-          <t>OnmmDvKS</t>
+          <t>n5LaWeHr</t>
         </is>
       </c>
       <c r="FE3" t="inlineStr">
         <is>
-          <t>camblan axel</t>
-        </is>
-      </c>
-      <c r="FF3" t="inlineStr">
-        <is>
-          <t>hnER3xyT</t>
-        </is>
-      </c>
-      <c r="FG3" t="inlineStr">
-        <is>
-          <t>del castillo romain</t>
+          <t>sanson morgan</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zoZtwwYp</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2JHnrhNN</t>
+          <t>xMzvOmz3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gurtner regis</t>
+          <t>desmas arthur</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>buhL1Onn</t>
+          <t>Spy29tSF</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>corchia sebastien</t>
+          <t>nego loic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>xQJX0yQr</t>
+          <t>lGwSlg7D</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>bakayoko siaka</t>
+          <t>sangante arouna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6944n3Fq</t>
+          <t>hpstm6bQ</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>fofana mamadou 1998</t>
+          <t>salmier yoann</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4vxs1tdM</t>
+          <t>pMUGrcL4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>vita remy</t>
+          <t>lloris gautier</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>QgfweBPT</t>
+          <t>lIu2iTW5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gene owen</t>
+          <t>operi christopher</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>UBVYZus6</t>
+          <t>2Lq1p0u3</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>kaiboue kylian</t>
+          <t>ndiaye rassoul</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6w822cDk</t>
+          <t>21pKzBVs</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>leautey antoine</t>
+          <t>kechta yassine</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>zJWNDWUp</t>
+          <t>jDX28pzf</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>lutin rayan</t>
+          <t>toure abdoulaye</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rySVdKzI</t>
+          <t>ULZGhzIc</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>mubundu manitu messy</t>
+          <t>targhalline oussama</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>MFLAEEaI</t>
+          <t>futJjw50</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>mafouta louis</t>
+          <t>soumare issa</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>fkOg2Gqj</t>
+          <t>63zhY82M</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>mvogo yvon</t>
+          <t>leon donovan</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Est8UaLc</t>
+          <t>IaxyOwfg</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>igor silva</t>
+          <t>hoever ki jana</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>4nPjVrMS</t>
+          <t>4b1ioyMB</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>mendy formose</t>
+          <t>jubal</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>bLU8KtEd</t>
+          <t>CtMie175</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>talbi montassar</t>
+          <t>osho gabriel</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>O2h5w23g</t>
+          <t>bNxDifo4</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>ngameni darline zidane</t>
+          <t>joly paul</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8vMxrdie</t>
+          <t>K8xLQNgH</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>mvuka joel</t>
+          <t>raveloson rayan</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>YJhgLOwk</t>
+          <t>2TDOiuxH</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>ponceau julien</t>
+          <t>owusu elisha</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>WzrmHcCA</t>
+          <t>GMQ5M5dn</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>abergel laurent</t>
+          <t>perrin gaetan</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>pOt3Q6yb</t>
+          <t>Sr1MZT2U</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>pagis pablo</t>
+          <t>traore hamed</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>fHMXip22</t>
+          <t>ALL2QBYu</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>kroupi eli junior</t>
+          <t>sinayoko lassine</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>zTOOlq65</t>
+          <t>p0ZNpI36</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>aiyegun tosin</t>
+          <t>bair thelonius</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>EPx2q8TS</t>
+          <t>A3L0pzbI</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>boya frank</t>
+          <t>casimir josue</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>fsQHmhiO</t>
+          <t>jevYFpy7</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>carroll andy</t>
+          <t>gorgelin mathieu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>UFCV4BZC</t>
+          <t>E7LMto5e</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>chabane amine</t>
+          <t>grandsir samuel</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>SIEq4Qzk</t>
+          <t>niaa7gUb</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>dao elyess</t>
+          <t>housni ilyes</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>hKnfwbm3</t>
+          <t>n5pKaQsh</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>fofana ibrahim cheick junior</t>
+          <t>joujou antoine</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>pWfVw1vj</t>
+          <t>AgmwPJ36</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>sauvage alexis</t>
+          <t>kuzyayev daler</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>CWFxV8dL</t>
+          <t>6H79Cl3d</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>touho mathis</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
+          <t>mosengo daren nbenbege</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2FPUx4e9</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>ngoura steve</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>v9ih1MV1</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>zouaoui yanis</t>
+        </is>
+      </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>z1as6ykH</t>
+          <t>fo9YVp8o</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>adjei nathaniel</t>
+          <t>akpa clement</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>hMJmRmWR</t>
+          <t>b1YrLw2G</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>avom arthur</t>
+          <t>aye florian</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>GjVTxPsc</t>
+          <t>GGj5ySgp</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>james isaac</t>
+          <t>danois kevin</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>hbh3pcUj</t>
+          <t>zZttO6ua</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>kalulu gedeon</t>
+          <t>de percin theo</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>p6J3hnvC</t>
+          <t>6X2uao2q</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>le bris theo</t>
+          <t>diomande sinaly</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>KAxiV8Bj</t>
+          <t>xQpouO6n</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>leroy benjamin</t>
+          <t>diousse assane</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>YByvtrWm</t>
+          <t>Ofn7ZeU2</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>soumano sambou</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr"/>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
+          <t>maddy eros</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>8Ka0CoOm</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>pellenard theo</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>EwDMztdS</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>viadere ben</t>
+        </is>
+      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>fsQHmhiO</t>
+          <t>A3L0pzbI</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>carroll andy</t>
+          <t>casimir josue</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>fsQHmhiO</t>
+          <t>A3L0pzbI</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>carroll andy</t>
+          <t>casimir josue</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>rySVdKzI</t>
+          <t>2Lq1p0u3</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>mubundu manitu messy</t>
+          <t>ndiaye rassoul</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>EPx2q8TS</t>
+          <t>n5pKaQsh</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>boya frank</t>
+          <t>joujou antoine</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>EPx2q8TS</t>
+          <t>n5pKaQsh</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>boya frank</t>
+          <t>joujou antoine</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>zJWNDWUp</t>
+          <t>futJjw50</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>lutin rayan</t>
+          <t>soumare issa</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>hKnfwbm3</t>
+          <t>AgmwPJ36</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>fofana ibrahim cheick junior</t>
+          <t>kuzyayev daler</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>hKnfwbm3</t>
+          <t>AgmwPJ36</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>fofana ibrahim cheick junior</t>
+          <t>kuzyayev daler</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>UBVYZus6</t>
+          <t>21pKzBVs</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>kaiboue kylian</t>
+          <t>kechta yassine</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr"/>
@@ -3256,116 +3330,172 @@
       <c r="CY4" t="inlineStr"/>
       <c r="CZ4" t="inlineStr"/>
       <c r="DA4" t="inlineStr"/>
-      <c r="DB4" t="inlineStr">
-        <is>
-          <t>YByvtrWm</t>
-        </is>
-      </c>
-      <c r="DC4" t="inlineStr">
-        <is>
-          <t>soumano sambou</t>
-        </is>
-      </c>
-      <c r="DD4" t="inlineStr">
-        <is>
-          <t>YByvtrWm</t>
-        </is>
-      </c>
-      <c r="DE4" t="inlineStr">
-        <is>
-          <t>soumano sambou</t>
-        </is>
-      </c>
-      <c r="DF4" t="inlineStr">
-        <is>
-          <t>fHMXip22</t>
-        </is>
-      </c>
-      <c r="DG4" t="inlineStr">
-        <is>
-          <t>kroupi eli junior</t>
-        </is>
-      </c>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>hMJmRmWR</t>
+          <t>fo9YVp8o</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
         <is>
-          <t>avom arthur</t>
+          <t>akpa clement</t>
         </is>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>hMJmRmWR</t>
+          <t>fo9YVp8o</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>avom arthur</t>
+          <t>akpa clement</t>
         </is>
       </c>
       <c r="DL4" t="inlineStr">
         <is>
-          <t>pOt3Q6yb</t>
+          <t>p0ZNpI36</t>
         </is>
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>pagis pablo</t>
+          <t>bair thelonius</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>p6J3hnvC</t>
+          <t>GGj5ySgp</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>le bris theo</t>
+          <t>danois kevin</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
         <is>
-          <t>p6J3hnvC</t>
+          <t>GGj5ySgp</t>
         </is>
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>le bris theo</t>
+          <t>danois kevin</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
         <is>
-          <t>8vMxrdie</t>
+          <t>GMQ5M5dn</t>
         </is>
       </c>
       <c r="DS4" t="inlineStr">
         <is>
-          <t>mvuka joel</t>
-        </is>
-      </c>
-      <c r="DT4" t="inlineStr"/>
-      <c r="DU4" t="inlineStr"/>
-      <c r="DV4" t="inlineStr"/>
-      <c r="DW4" t="inlineStr"/>
-      <c r="DX4" t="inlineStr"/>
-      <c r="DY4" t="inlineStr"/>
-      <c r="DZ4" t="inlineStr"/>
-      <c r="EA4" t="inlineStr"/>
-      <c r="EB4" t="inlineStr"/>
-      <c r="EC4" t="inlineStr"/>
-      <c r="ED4" t="inlineStr"/>
-      <c r="EE4" t="inlineStr"/>
-      <c r="EF4" t="inlineStr"/>
-      <c r="EG4" t="inlineStr"/>
-      <c r="EH4" t="inlineStr"/>
-      <c r="EI4" t="inlineStr"/>
-      <c r="EJ4" t="inlineStr"/>
-      <c r="EK4" t="inlineStr"/>
-      <c r="EL4" t="inlineStr"/>
-      <c r="EM4" t="inlineStr"/>
+          <t>perrin gaetan</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>6X2uao2q</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>diomande sinaly</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>6X2uao2q</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>diomande sinaly</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>CtMie175</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>osho gabriel</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>b1YrLw2G</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>aye florian</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>b1YrLw2G</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>aye florian</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>ALL2QBYu</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>sinayoko lassine</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>Ofn7ZeU2</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>maddy eros</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>Ofn7ZeU2</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>maddy eros</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>bNxDifo4</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>joly paul</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>4GZwFq7E</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>logbo andy elysee</t>
+        </is>
+      </c>
       <c r="EN4" t="inlineStr"/>
       <c r="EO4" t="inlineStr"/>
       <c r="EP4" t="inlineStr"/>
@@ -3374,657 +3504,799 @@
       <c r="ES4" t="inlineStr"/>
       <c r="ET4" t="inlineStr"/>
       <c r="EU4" t="inlineStr"/>
-      <c r="EV4" t="inlineStr"/>
-      <c r="EW4" t="inlineStr"/>
-      <c r="EX4" t="inlineStr"/>
-      <c r="EY4" t="inlineStr"/>
-      <c r="EZ4" t="inlineStr"/>
-      <c r="FA4" t="inlineStr"/>
-      <c r="FB4" t="inlineStr"/>
-      <c r="FC4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr">
+        <is>
+          <t>vJSrWUkm</t>
+        </is>
+      </c>
+      <c r="EW4" t="inlineStr">
+        <is>
+          <t>agouzoul saad</t>
+        </is>
+      </c>
+      <c r="EX4" t="inlineStr">
+        <is>
+          <t>2TkiOPy5</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
+          <t>mensah gideon</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>UZG5ZtWh</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>n gatta ange</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>xCwPADx0</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>onaiwu ado</t>
+        </is>
+      </c>
       <c r="FD4" t="inlineStr"/>
       <c r="FE4" t="inlineStr"/>
-      <c r="FF4" t="inlineStr"/>
-      <c r="FG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8lUzaKf4</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>tCw122Zu</t>
+          <t>xCg7OFVE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>oukidja alexandre</t>
+          <t>diouf yehvann</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YaVQrOB5</t>
+          <t>SvBsKAPE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>colin maxime</t>
+          <t>buta aurelio</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>jZhhxxLu</t>
+          <t>zBgW9dak</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>traore ismael</t>
+          <t>okumu joseph</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AuzyopRB</t>
+          <t>fRbu2Opo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>udol matthieu</t>
+          <t>agbadou emmanuel</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ncoSpPJ3</t>
+          <t>W2ZQhrQI</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>kouao koffi</t>
+          <t>sangui nhoa</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>GlPxp8Ek</t>
+          <t>2LonY10K</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>deminguet jessy</t>
+          <t>munetsi nyasha</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>06rZTKMc</t>
+          <t>MskdO4tG</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>hein gauthier</t>
+          <t>atangana edoa valentin</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>21NXX0AU</t>
+          <t>Yg2zH6de</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>cande fali</t>
+          <t>fofana yaya kader</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>OKRPP19G</t>
+          <t>j9vuLu2S</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>jallow ablie</t>
+          <t>junya ito</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>v9UFU7UB</t>
+          <t>jeOb1FYh</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>sane ibou</t>
+          <t>diakite oumar</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>E5Ot0kk3</t>
+          <t>ttEUhyfq</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>sabaly cheikh tidiane</t>
+          <t>nakamura keito</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Whzw3G5K</t>
+          <t>A5YHqogH</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>samassa mamadou</t>
+          <t>mandanda steve</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>KbXo1rjj</t>
+          <t>Aok70rK9</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>vargas thibault</t>
+          <t>hateboer hans</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lIDA7uHl</t>
+          <t>lIN7BM8b</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ouaneh peter</t>
+          <t>ostigard leo</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Wh6NlULE</t>
+          <t>0jUAc9hA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>tavares yohan</t>
+          <t>wooh christopher</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>QyXR4UTq</t>
+          <t>WQprkBYj</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>kouassi christ owen</t>
+          <t>truffert adrien</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>h2wDEAtM</t>
+          <t>Uwj8SaVP</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>cherni amine</t>
+          <t>blas ludovic</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>xjWxEtds</t>
+          <t>Q5uPXvlA</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>sanna sam</t>
+          <t>matusiwa azor</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0IAHPMVG</t>
+          <t>IPBMorSq</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>thomas titouan</t>
+          <t>kamara glen</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2JZ0HH6Q</t>
+          <t>nejuxKZl</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>sellouki malik</t>
+          <t>gronbaek albert</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>W2tc6ZMa</t>
+          <t>xC9K9Yug</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>zohi kevin</t>
+          <t>kalimuendo arnaud</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>IZHMuCIC</t>
+          <t>K0zFVdU8</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>doucoure sirine</t>
+          <t>gouiri amine</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>6D2EWpmi</t>
+          <t>nNs2cZ1e</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>asoro joel</t>
+          <t>bamba mohamed aboubakar</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>UqhfTgL6</t>
+          <t>vBVl3fPN</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>bokele mputu morgan</t>
+          <t>bojang adama</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>xdl3kAtK</t>
+          <t>WfOJXqJA</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>diallo papa amadou</t>
+          <t>de smet thibault</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>tE85H9db</t>
+          <t>hhMsOIeH</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>nduquidi joseph</t>
+          <t>diakhon mamadou</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>O8reaWmD</t>
+          <t>tSf0YZjE</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>sane sadibou</t>
+          <t>khadra reda</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>OADbJzj2</t>
+          <t>Eol9RH7r</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>sy pape</t>
+          <t>kipre cedric</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>EX50xRu9</t>
+          <t>EyJTU6I9</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>toure alpha</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
+          <t>olliero alexandre</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>8fTnn97m</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>salama amine</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>pWuFUK4s</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>teuma teddy</t>
+        </is>
+      </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>Amfeubd3</t>
+          <t>2T5az5TR</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>adilehou moise</t>
+          <t>assignon lorenz</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>OpjMuJEk</t>
+          <t>dlwRDO07</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>goncalves anthony</t>
+          <t>cisse djaoui</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>zXm9ns79</t>
+          <t>nBYc98Fs</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>hautbois maxime</t>
+          <t>faye mikayil</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0K3veiZ5</t>
+          <t>vkDxNkmn</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>kokolo williams</t>
+          <t>gallon gauthier</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>h0KBtgkc</t>
+          <t>WA3PZWCE</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>martins lois</t>
+          <t>gomez andres</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>UBp43Hs9</t>
+          <t>j3EexUWf</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>roye jimmy</t>
+          <t>james jordan</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>px7nJZss</t>
+          <t>8EP6jKUI</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>tell jordan</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr"/>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="inlineStr"/>
+          <t>meister henrik</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>Ioy3ZkK1</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>santamaria baptiste</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>bi8NhkWD</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>seidu alidu</t>
+        </is>
+      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>xdl3kAtK</t>
+          <t>8fTnn97m</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>diallo papa amadou</t>
+          <t>salama amine</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>xdl3kAtK</t>
+          <t>8fTnn97m</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>diallo papa amadou</t>
+          <t>salama amine</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>21NXX0AU</t>
+          <t>jeOb1FYh</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>cande fali</t>
+          <t>diakite oumar</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>6D2EWpmi</t>
+          <t>pWuFUK4s</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>asoro joel</t>
+          <t>teuma teddy</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>6D2EWpmi</t>
+          <t>pWuFUK4s</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>asoro joel</t>
+          <t>teuma teddy</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>v9UFU7UB</t>
+          <t>Yg2zH6de</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>sane ibou</t>
+          <t>fofana yaya kader</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>tE85H9db</t>
+          <t>tSf0YZjE</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>nduquidi joseph</t>
+          <t>khadra reda</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>tE85H9db</t>
+          <t>tSf0YZjE</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>nduquidi joseph</t>
+          <t>khadra reda</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>GlPxp8Ek</t>
+          <t>j9vuLu2S</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>deminguet jessy</t>
-        </is>
-      </c>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr"/>
-      <c r="DA5" t="inlineStr"/>
+          <t>junya ito</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>Eol9RH7r</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>kipre cedric</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>Eol9RH7r</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>kipre cedric</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>ttEUhyfq</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>nakamura keito</t>
+        </is>
+      </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>Amfeubd3</t>
+          <t>WfOJXqJA</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
         <is>
-          <t>adilehou moise</t>
+          <t>de smet thibault</t>
         </is>
       </c>
       <c r="DD5" t="inlineStr">
         <is>
-          <t>Amfeubd3</t>
+          <t>WfOJXqJA</t>
         </is>
       </c>
       <c r="DE5" t="inlineStr">
         <is>
-          <t>adilehou moise</t>
+          <t>de smet thibault</t>
         </is>
       </c>
       <c r="DF5" t="inlineStr">
         <is>
-          <t>lIDA7uHl</t>
+          <t>SvBsKAPE</t>
         </is>
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>ouaneh peter</t>
+          <t>buta aurelio</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>px7nJZss</t>
+          <t>WA3PZWCE</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>tell jordan</t>
+          <t>gomez andres</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
         <is>
-          <t>px7nJZss</t>
+          <t>WA3PZWCE</t>
         </is>
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>tell jordan</t>
+          <t>gomez andres</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>IZHMuCIC</t>
+          <t>xC9K9Yug</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
         <is>
-          <t>doucoure sirine</t>
+          <t>kalimuendo arnaud</t>
         </is>
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>h0KBtgkc</t>
+          <t>bi8NhkWD</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>martins lois</t>
+          <t>seidu alidu</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>h0KBtgkc</t>
+          <t>bi8NhkWD</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>martins lois</t>
+          <t>seidu alidu</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>W2tc6ZMa</t>
+          <t>WQprkBYj</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
         <is>
-          <t>zohi kevin</t>
+          <t>truffert adrien</t>
         </is>
       </c>
       <c r="DT5" t="inlineStr">
         <is>
-          <t>UBp43Hs9</t>
+          <t>2T5az5TR</t>
         </is>
       </c>
       <c r="DU5" t="inlineStr">
         <is>
-          <t>roye jimmy</t>
+          <t>assignon lorenz</t>
         </is>
       </c>
       <c r="DV5" t="inlineStr">
         <is>
-          <t>UBp43Hs9</t>
+          <t>2T5az5TR</t>
         </is>
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>roye jimmy</t>
+          <t>assignon lorenz</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>2JZ0HH6Q</t>
+          <t>Aok70rK9</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>sellouki malik</t>
+          <t>hateboer hans</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>0K3veiZ5</t>
+          <t>Ioy3ZkK1</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>kokolo williams</t>
+          <t>santamaria baptiste</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>0K3veiZ5</t>
+          <t>Ioy3ZkK1</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>kokolo williams</t>
+          <t>santamaria baptiste</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>h2wDEAtM</t>
+          <t>IPBMorSq</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>cherni amine</t>
-        </is>
-      </c>
-      <c r="EF5" t="inlineStr"/>
-      <c r="EG5" t="inlineStr"/>
-      <c r="EH5" t="inlineStr"/>
-      <c r="EI5" t="inlineStr"/>
-      <c r="EJ5" t="inlineStr"/>
-      <c r="EK5" t="inlineStr"/>
-      <c r="EL5" t="inlineStr"/>
-      <c r="EM5" t="inlineStr"/>
-      <c r="EN5" t="inlineStr"/>
-      <c r="EO5" t="inlineStr"/>
-      <c r="EP5" t="inlineStr"/>
-      <c r="EQ5" t="inlineStr"/>
+          <t>kamara glen</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>8EP6jKUI</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>meister henrik</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>8EP6jKUI</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>meister henrik</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>Uwj8SaVP</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>blas ludovic</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>4nBZRS2T</t>
+        </is>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>akieme sergio</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>63FSiIkD</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>daramy mohammed</t>
+        </is>
+      </c>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t>MoRIjLE2</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>kone abdoul</t>
+        </is>
+      </c>
       <c r="ER5" t="inlineStr"/>
       <c r="ES5" t="inlineStr"/>
       <c r="ET5" t="inlineStr"/>
       <c r="EU5" t="inlineStr"/>
-      <c r="EV5" t="inlineStr"/>
-      <c r="EW5" t="inlineStr"/>
+      <c r="EV5" t="inlineStr">
+        <is>
+          <t>CngQQtwt</t>
+        </is>
+      </c>
+      <c r="EW5" t="inlineStr">
+        <is>
+          <t>alemdar dogan</t>
+        </is>
+      </c>
       <c r="EX5" t="inlineStr"/>
       <c r="EY5" t="inlineStr"/>
       <c r="EZ5" t="inlineStr"/>
@@ -4033,8 +4305,1532 @@
       <c r="FC5" t="inlineStr"/>
       <c r="FD5" t="inlineStr"/>
       <c r="FE5" t="inlineStr"/>
-      <c r="FF5" t="inlineStr"/>
-      <c r="FG5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>WYUNrwz4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>kohn philipp</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Sbk0VFPJ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>teze jordan</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ym8dZot0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>singo wilfried</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>QkOX3B5N</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>mawissa christian</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>x0We5RpI</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ouattara kassoum</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>zsPNUcJd</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>magassa soungoutou</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>d23lOQrL</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>zakaria denis</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0UP6MLGJ</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>akliouche maghnes</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>hIwtloy3</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>minamino takumi</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>S2dMSJX1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>ben seghir eliesse</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>rVZLmUsU</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>balgun folarin</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6L93gfZq</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>samba brice</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>dtKPzgw3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>gradit jonathan</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00ElbXx5</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>khusanov abdukodir</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>tEuOUQT3</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>medina facundo</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Of80t1aH</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>aguilar ruben</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>4bTqh1H2</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>thomasson adrien</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>IiBJCs82</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>diouf andy</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>vFCwyxSO</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>chavez jhoanner</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>pdcd6LXR</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>zaroury anass</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>AgROGWlt</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>sotoca florian</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>400jX4xg</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>said wesley</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>dr5D8pxI</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>caio henrique</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>lbPmGop2</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>diatta krepin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>CpKkPKuP</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>embolo breel</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>WSP08bVp</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>golovin aleksandr</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>t41NlDfO</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>ilenikhena george</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>UXQPdpOB</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>kehrer thilo</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>OfVIIvoN</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>lienard yann</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>zuFTjQI5</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>salisu mohammed</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>OjKXB6ns</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>vanderson</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>jwOj3L3C</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>frankowski przemyslaw</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>00OiLLms</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>labeau remy</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>SAjbGhS3</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>mendy nampalys</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>vD33dp4n</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>nzola m bala</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>2qEVnrLJ</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>ojediran hamzat</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>zLUKPOh2</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>pereira da costa david</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>4EdoEoil</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>petric denis</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>zZ3dzMX8</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>sarr malang</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>rmhmN1WA</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>satriano martin</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>OjKXB6ns</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>vanderson</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>OjKXB6ns</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>vanderson</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>Sbk0VFPJ</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>teze jordan</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>CpKkPKuP</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>embolo breel</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>CpKkPKuP</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>embolo breel</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>rVZLmUsU</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>balgun folarin</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>t41NlDfO</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>ilenikhena george</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>t41NlDfO</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>ilenikhena george</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>S2dMSJX1</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>ben seghir eliesse</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>dr5D8pxI</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>caio henrique</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>dr5D8pxI</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>caio henrique</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>x0We5RpI</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>ouattara kassoum</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>WSP08bVp</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>golovin aleksandr</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>WSP08bVp</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>golovin aleksandr</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>QkOX3B5N</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>mawissa christian</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>zLUKPOh2</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t>pereira da costa david</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>zLUKPOh2</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>pereira da costa david</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr">
+        <is>
+          <t>pdcd6LXR</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>zaroury anass</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>00OiLLms</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>labeau remy</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>00OiLLms</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>labeau remy</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>400jX4xg</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>said wesley</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>2qEVnrLJ</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>ojediran hamzat</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>2qEVnrLJ</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>ojediran hamzat</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>4bTqh1H2</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>thomasson adrien</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>jwOj3L3C</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>frankowski przemyslaw</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>jwOj3L3C</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>frankowski przemyslaw</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>Of80t1aH</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>aguilar ruben</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>rmhmN1WA</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>satriano martin</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>rmhmN1WA</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>satriano martin</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>vFCwyxSO</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>chavez jhoanner</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>boBGHitI</t>
+        </is>
+      </c>
+      <c r="EM6" t="inlineStr">
+        <is>
+          <t>camara lamine</t>
+        </is>
+      </c>
+      <c r="EN6" t="inlineStr">
+        <is>
+          <t>2yi87XSs</t>
+        </is>
+      </c>
+      <c r="EO6" t="inlineStr">
+        <is>
+          <t>coulibaly mamadou</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
+          <t>EJpPkLtD</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t>diop edan</t>
+        </is>
+      </c>
+      <c r="ER6" t="inlineStr"/>
+      <c r="ES6" t="inlineStr"/>
+      <c r="ET6" t="inlineStr"/>
+      <c r="EU6" t="inlineStr"/>
+      <c r="EV6" t="inlineStr">
+        <is>
+          <t>KIP4iWK5</t>
+        </is>
+      </c>
+      <c r="EW6" t="inlineStr">
+        <is>
+          <t>cabot jimmy</t>
+        </is>
+      </c>
+      <c r="EX6" t="inlineStr">
+        <is>
+          <t>f3mqZ2x6</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
+          <t>el aynaoui neil</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
+          <t>CSjPEukJ</t>
+        </is>
+      </c>
+      <c r="FA6" t="inlineStr">
+        <is>
+          <t>machado deiver</t>
+        </is>
+      </c>
+      <c r="FB6" t="inlineStr"/>
+      <c r="FC6" t="inlineStr"/>
+      <c r="FD6" t="inlineStr"/>
+      <c r="FE6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>v3qqsoQi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>restes guillaume</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Gh4c98Hd</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>cresswell charlie</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4vagAHJd</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nicolaisen rasmus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>S44zFHdC</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>mckenzie mark</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>d2T8jid4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>donnum aron</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ILJ8o9a3</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>sierro vincent</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4UatnyW3</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>casseres cristian</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>8lmlZBv6</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>suazo gabriel</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>OrzIGzrL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>aboukhlal zakaria</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>25Lm5dfs</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>gboho yann</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>d6nU7y6U</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>magri frank</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>rcbM0Dd8</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>rulli geronimo</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>rNLU0jIl</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>murillo michael</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Wvb8v5p5</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>cornelius derek</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>8YhWSbAS</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>brassier lilian</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>tvuaMWgc</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>merlin quentin</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>ITwS8wMo</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>hojbjerg pierre emile</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>nZs03zT2</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>kondogbia geoffrey</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>hxe108Jl</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>greenwood mason</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>lxSgSRDd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>harit amine</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>dU3VTnID</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>luis henrique</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>8jdHWf50</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>wahi sepe elye</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>rsukrrUF</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>akdag umit</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>zwDOyrZu</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>babicka shavy</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lAPckxbM</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>dominguez alex</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>IcR3roH8</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>genreau denis</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>ppfe4v67</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>kamanzi waren</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>nLnr7gpC</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>king joshua</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>v71VNtNg</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>methalie dayann</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>IPBGPtwU</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>schmidt niklas</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>EJYoIGzl</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>sidibe djibril</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>YisRM9NA</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>abdallah keyliane</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>GGTSMhui</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>de lange jeffrey</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>dYFeVggU</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>lirola pol</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>d0bSRUiP</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>maupay neal</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>xbLpmH22</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>meite abdoul</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>pQEvn0aK</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>rongier valentin</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>WQQaRzMF</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>rowe jon</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>YZTn9sgp</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>sternal enzo</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>EJYoIGzl</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>sidibe djibril</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>EJYoIGzl</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>sidibe djibril</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>Gh4c98Hd</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>cresswell charlie</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>zwDOyrZu</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>babicka shavy</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>zwDOyrZu</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>babicka shavy</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>4UatnyW3</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>casseres cristian</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>ppfe4v67</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>kamanzi waren</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>ppfe4v67</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>kamanzi waren</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>OrzIGzrL</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>aboukhlal zakaria</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>nLnr7gpC</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>king joshua</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>nLnr7gpC</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>king joshua</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>d2T8jid4</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>donnum aron</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>IPBGPtwU</t>
+        </is>
+      </c>
+      <c r="DC7" t="inlineStr">
+        <is>
+          <t>schmidt niklas</t>
+        </is>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>IPBGPtwU</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>schmidt niklas</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>25Lm5dfs</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>gboho yann</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>WQQaRzMF</t>
+        </is>
+      </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t>rowe jon</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>WQQaRzMF</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>rowe jon</t>
+        </is>
+      </c>
+      <c r="DL7" t="inlineStr">
+        <is>
+          <t>dU3VTnID</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>luis henrique</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>0S6Hz5ji</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>carboni valentin</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>lxSgSRDd</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>harit amine</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>d0bSRUiP</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>maupay neal</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>d0bSRUiP</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>maupay neal</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>8jdHWf50</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>wahi sepe elye</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>xbLpmH22</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>meite abdoul</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>xbLpmH22</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>meite abdoul</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>ITwS8wMo</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>hojbjerg pierre emile</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
+        <is>
+          <t>pQEvn0aK</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>rongier valentin</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>pQEvn0aK</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>rongier valentin</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>nZs03zT2</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>kondogbia geoffrey</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr"/>
+      <c r="EM7" t="inlineStr"/>
+      <c r="EN7" t="inlineStr"/>
+      <c r="EO7" t="inlineStr"/>
+      <c r="EP7" t="inlineStr"/>
+      <c r="EQ7" t="inlineStr"/>
+      <c r="ER7" t="inlineStr"/>
+      <c r="ES7" t="inlineStr"/>
+      <c r="ET7" t="inlineStr"/>
+      <c r="EU7" t="inlineStr"/>
+      <c r="EV7" t="inlineStr">
+        <is>
+          <t>MkgjOoBG</t>
+        </is>
+      </c>
+      <c r="EW7" t="inlineStr">
+        <is>
+          <t>kone ismael</t>
+        </is>
+      </c>
+      <c r="EX7" t="inlineStr">
+        <is>
+          <t>jXMIit0S</t>
+        </is>
+      </c>
+      <c r="EY7" t="inlineStr">
+        <is>
+          <t>moumbagna faris</t>
+        </is>
+      </c>
+      <c r="EZ7" t="inlineStr">
+        <is>
+          <t>2TItKacj</t>
+        </is>
+      </c>
+      <c r="FA7" t="inlineStr">
+        <is>
+          <t>nadir bilal</t>
+        </is>
+      </c>
+      <c r="FB7" t="inlineStr"/>
+      <c r="FC7" t="inlineStr"/>
+      <c r="FD7" t="inlineStr"/>
+      <c r="FE7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EM2"/>
+  <dimension ref="A1:EA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,949 +911,829 @@
       </c>
       <c r="CT1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_home_13</t>
+          <t>id_player_sub_enter_away_1</t>
         </is>
       </c>
       <c r="CU1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_home_13</t>
+          <t>player_name_sub_enter_away_1</t>
         </is>
       </c>
       <c r="CV1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_home_14</t>
+          <t>id_player_sub_enter_away_2</t>
         </is>
       </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_home_14</t>
+          <t>player_name_sub_enter_away_2</t>
         </is>
       </c>
       <c r="CX1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_home_15</t>
+          <t>id_player_sub_enter_away_3</t>
         </is>
       </c>
       <c r="CY1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_home_15</t>
+          <t>player_name_sub_enter_away_3</t>
         </is>
       </c>
       <c r="CZ1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_1</t>
+          <t>id_player_sub_enter_away_4</t>
         </is>
       </c>
       <c r="DA1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_1</t>
+          <t>player_name_sub_enter_away_4</t>
         </is>
       </c>
       <c r="DB1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_2</t>
+          <t>id_player_sub_enter_away_5</t>
         </is>
       </c>
       <c r="DC1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_2</t>
+          <t>player_name_sub_enter_away_5</t>
         </is>
       </c>
       <c r="DD1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_3</t>
+          <t>id_player_sub_enter_away_6</t>
         </is>
       </c>
       <c r="DE1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_3</t>
+          <t>player_name_sub_enter_away_6</t>
         </is>
       </c>
       <c r="DF1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_4</t>
+          <t>id_player_sub_enter_away_7</t>
         </is>
       </c>
       <c r="DG1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_4</t>
+          <t>player_name_sub_enter_away_7</t>
         </is>
       </c>
       <c r="DH1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_5</t>
+          <t>id_player_sub_enter_away_8</t>
         </is>
       </c>
       <c r="DI1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_5</t>
+          <t>player_name_sub_enter_away_8</t>
         </is>
       </c>
       <c r="DJ1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_6</t>
+          <t>id_player_sub_enter_away_9</t>
         </is>
       </c>
       <c r="DK1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_6</t>
+          <t>player_name_sub_enter_away_9</t>
         </is>
       </c>
       <c r="DL1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_7</t>
+          <t>id_player_sub_enter_away_10</t>
         </is>
       </c>
       <c r="DM1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_7</t>
+          <t>player_name_sub_enter_away_10</t>
         </is>
       </c>
       <c r="DN1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_8</t>
+          <t>id_player_sub_enter_away_11</t>
         </is>
       </c>
       <c r="DO1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_8</t>
+          <t>player_name_sub_enter_away_11</t>
         </is>
       </c>
       <c r="DP1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_9</t>
+          <t>id_player_sub_enter_away_12</t>
         </is>
       </c>
       <c r="DQ1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_9</t>
+          <t>player_name_sub_enter_away_12</t>
         </is>
       </c>
       <c r="DR1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_10</t>
+          <t>id_player_sub_enter_away_13</t>
         </is>
       </c>
       <c r="DS1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_10</t>
+          <t>player_name_sub_enter_away_13</t>
         </is>
       </c>
       <c r="DT1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_11</t>
+          <t>id_player_sub_enter_away_14</t>
         </is>
       </c>
       <c r="DU1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_11</t>
+          <t>player_name_sub_enter_away_14</t>
         </is>
       </c>
       <c r="DV1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_12</t>
+          <t>id_player_sub_enter_away_15</t>
         </is>
       </c>
       <c r="DW1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_12</t>
+          <t>player_name_sub_enter_away_15</t>
         </is>
       </c>
       <c r="DX1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_13</t>
+          <t>id_player_miss_home_1</t>
         </is>
       </c>
       <c r="DY1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_13</t>
+          <t>player_name_miss_home_1</t>
         </is>
       </c>
       <c r="DZ1" s="1" t="inlineStr">
         <is>
-          <t>id_player_sub_enter_away_14</t>
+          <t>id_player_miss_away_1</t>
         </is>
       </c>
       <c r="EA1" s="1" t="inlineStr">
         <is>
-          <t>player_name_sub_enter_away_14</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_sub_enter_away_15</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
           <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2g2J0IEs</t>
+          <t>f5f1oGre</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qg47cicT</t>
+          <t>UqwxErXc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>boucher zacharie</t>
+          <t>kamara bingourou</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nkt4zHnF</t>
+          <t>UVcaeNxh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>boura ismael</t>
+          <t>gaspar jordy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>jTCO0CRG</t>
+          <t>f77lo10C</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>monfray adrien</t>
+          <t>ahoussou kouadio guy ange</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>UmQAaj9U</t>
+          <t>A1JE6XmB</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>diaz michel</t>
+          <t>ruiz jean</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>j1nHmY4P</t>
+          <t>xUaIYbZa</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>gozzi paolo</t>
+          <t>koudou therence</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>jqI1zNGn</t>
+          <t>UTeVGQBo</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>irie cyriaque</t>
+          <t>ngom oumar</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>OAOSz9F9</t>
+          <t>K0sjhCJO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>balde thierno</t>
+          <t>mohamed iyad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>42xsAKpa</t>
+          <t>ManhCoID</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>adeline martin</t>
+          <t>arconte tairyk</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>fkSVDJ7k</t>
+          <t>GjoN5Ete</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>nonge boende joseph</t>
+          <t>mille antoine</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>QaynB0J3</t>
+          <t>CrYHlkps</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>said rafiki</t>
+          <t>mboup pathe</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>zuiN9zaU</t>
+          <t>GUQFSOu2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>ba pape ibnou</t>
+          <t>boutaib khalid</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Uc1khkvm</t>
+          <t>hz9iLSns</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>nkambadio obed</t>
+          <t>placide johnny</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>jcMPmwUo</t>
+          <t>x6p5H6p3</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>tourraine mathys</t>
+          <t>tavares dylan</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>8UK1HbMC</t>
+          <t>IwWAp1LB</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>mbow mamadou</t>
+          <t>guevara juan</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6Nrp053I</t>
+          <t>4C2mjUxk</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>kolodziejczak timothee</t>
+          <t>roncaglia anthony</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Ak6ZwNei</t>
+          <t>YosmxyVS</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>gaudin jules</t>
+          <t>guidi dominique</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>dvCqyKNu</t>
+          <t>dGEFacR1</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>doucet lohann</t>
+          <t>bohnert florian</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4QFT6q49</t>
+          <t>b9dIWhMU</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>lopez maxime</t>
+          <t>onana cyrille</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>zZWv9QAr</t>
+          <t>ronEz0Iq</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>camara adama</t>
+          <t>ducrocq tom</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>8zzd9I9p</t>
+          <t>EodMM41U</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>kebbal ilan</t>
+          <t>vincent christophe</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>MDGk7mZd</t>
+          <t>xr3SdJz4</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>krasso jean philippe</t>
+          <t>rodrigues clement</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>CIHpd5Na</t>
+          <t>vVf0mSM7</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>gory alimani</t>
+          <t>boutrah amine</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>dzY8Gcno</t>
+          <t>ImnpF5je</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>assoumou kouadou jaures</t>
+          <t>beusnard steeve</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>zwFrnSXF</t>
+          <t>SbqnArs2</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>dong kyliane</t>
+          <t>bobichon antonin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>tdNIZmPm</t>
+          <t>2afwUEQS</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>fage ryan</t>
+          <t>van boto kenji</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>vD9vUPLe</t>
+          <t>EJuazaLT</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>lemaitre nicolas</t>
+          <t>kante ousmane</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>xQzrR2fm</t>
+          <t>vyNtJpK2</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>m changama youssouf</t>
+          <t>kouassi xavier</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>63DHUXLG</t>
+          <t>Ollmu17h</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>mendes houboulang</t>
+          <t>njoh yonis</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>IHXHPyfp</t>
+          <t>0ID2g08S</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>ripart renaud</t>
+          <t>paradowski tao</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>pzIqHPOJ</t>
+          <t>4Ou8BC7i</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>dicko nouha</t>
+          <t>cisse lamine</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>jcnRT8Xf</t>
+          <t>0hzAGETn</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>hamel pierre yves</t>
+          <t>janneh jocelyn</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>YF5m5ItO</t>
+          <t>S8afnvrC</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>kante mohamadou</t>
+          <t>maggiotti julien</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>ULOxNwXn</t>
+          <t>UFy0eGZh</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>lopez julien</t>
+          <t>maisonnial anthony</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>6Ze5jFyJ</t>
+          <t>O4n6NMUE</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>marchetti vincent</t>
+          <t>meynadier tom</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>6Nb8GjF8</t>
+          <t>pfhFEyG5</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>riou remy</t>
+          <t>tomi felix</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>niLz9KKj</t>
+          <t>0f89SvvA</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>soumahoro aboubaka</t>
+          <t>tramoni lisandru</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>zwFrnSXF</t>
+          <t>ImnpF5je</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>dong kyliane</t>
+          <t>beusnard steeve</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>zwFrnSXF</t>
+          <t>ImnpF5je</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>dong kyliane</t>
+          <t>beusnard steeve</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>OAOSz9F9</t>
+          <t>UTeVGQBo</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>balde thierno</t>
+          <t>ngom oumar</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>IHXHPyfp</t>
+          <t>SbqnArs2</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>ripart renaud</t>
+          <t>bobichon antonin</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>IHXHPyfp</t>
+          <t>SbqnArs2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>ripart renaud</t>
+          <t>bobichon antonin</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>zuiN9zaU</t>
+          <t>GUQFSOu2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>ba pape ibnou</t>
+          <t>boutaib khalid</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>63DHUXLG</t>
+          <t>Ollmu17h</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>mendes houboulang</t>
+          <t>njoh yonis</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>63DHUXLG</t>
+          <t>Ollmu17h</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>mendes houboulang</t>
+          <t>njoh yonis</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>j1nHmY4P</t>
+          <t>GjoN5Ete</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>gozzi paolo</t>
+          <t>mille antoine</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>xQzrR2fm</t>
+          <t>2afwUEQS</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>m changama youssouf</t>
+          <t>van boto kenji</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>xQzrR2fm</t>
+          <t>2afwUEQS</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>m changama youssouf</t>
+          <t>van boto kenji</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>42xsAKpa</t>
+          <t>xUaIYbZa</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>adeline martin</t>
+          <t>koudou therence</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>dzY8Gcno</t>
+          <t>0hzAGETn</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>assoumou kouadou jaures</t>
+          <t>janneh jocelyn</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>dzY8Gcno</t>
+          <t>0hzAGETn</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>assoumou kouadou jaures</t>
+          <t>janneh jocelyn</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>jqI1zNGn</t>
+          <t>YosmxyVS</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>irie cyriaque</t>
+          <t>guidi dominique</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>jcnRT8Xf</t>
+          <t>0f89SvvA</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>hamel pierre yves</t>
+          <t>tramoni lisandru</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>jcnRT8Xf</t>
+          <t>0f89SvvA</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>hamel pierre yves</t>
+          <t>tramoni lisandru</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>CIHpd5Na</t>
+          <t>b9dIWhMU</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>gory alimani</t>
+          <t>onana cyrille</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>ULOxNwXn</t>
+          <t>O4n6NMUE</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>lopez julien</t>
+          <t>meynadier tom</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>ULOxNwXn</t>
+          <t>O4n6NMUE</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>lopez julien</t>
+          <t>meynadier tom</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>MDGk7mZd</t>
+          <t>x6p5H6p3</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>krasso jean philippe</t>
+          <t>tavares dylan</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>6Ze5jFyJ</t>
+          <t>pfhFEyG5</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>marchetti vincent</t>
+          <t>tomi felix</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>6Ze5jFyJ</t>
+          <t>pfhFEyG5</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>marchetti vincent</t>
+          <t>tomi felix</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>dvCqyKNu</t>
+          <t>xr3SdJz4</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>doucet lohann</t>
+          <t>rodrigues clement</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>niLz9KKj</t>
+          <t>S8afnvrC</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>soumahoro aboubaka</t>
+          <t>maggiotti julien</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>niLz9KKj</t>
+          <t>S8afnvrC</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>soumahoro aboubaka</t>
+          <t>maggiotti julien</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>4QFT6q49</t>
+          <t>EodMM41U</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>lopez maxime</t>
+          <t>vincent christophe</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>pzIqHPOJ</t>
+          <t>nwq413wg</t>
         </is>
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>dicko nouha</t>
+          <t>obiang johann</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>pzIqHPOJ</t>
+          <t>dSQ7Ps9s</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>dicko nouha</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>zZWv9QAr</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>camara adama</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>A7Ucux61</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>jean tahrat mehdi</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>hdJukE1U</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>alakouch sofiane</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>C4Q8WADc</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>chergui samir</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>8C7jzuf0</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>gueye lamine</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>b3WXEb7I</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>kore yoan</t>
+          <t>traore charles</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
+++ b/data/france/p6_deployment/missing/data_understanding/df_match_player_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1379 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:EG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_1</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_2</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_3</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_4</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_5</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_6</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_7</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_8</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_9</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_10</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_11</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_12</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_13</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_14</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_home_15</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_1</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_2</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_3</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_4</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_5</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_6</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_7</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_8</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_9</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_10</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_11</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_12</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_13</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_14</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_enter_away_15</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>4WNXteh2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4nR8LCCp</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sollacaro francois</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>d4NLQlPJ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>youssouf mohamed</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tWEjLiqi</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>bamba axel</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>j1uZ9TzE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ayessa jesah</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>MofSomLs</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>huard matthieu</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MT98e48G</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>jabol folcarelli tim</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>KrAz4afq</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>junior everson</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4Ug33NLF</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>anziani julien</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>dOX2dgkB</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>toure ben</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Otvrow2g</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>barreto mickael</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>OADbJzj2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>sy pape</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>O8reaWmD</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>sane sadibou</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ncoSpPJ3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kouao koffi</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>AuzyopRB</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>udol matthieu</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>jZhhxxLu</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>traore ismael</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>OKRPP19G</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>jallow ablie</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Is2SqL3S</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>stambouli benjamin</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>GlPxp8Ek</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>deminguet jessy</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>UqhfTgL6</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>bokele mputu morgan</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>E5Ot0kk3</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>sabaly cheikh tidiane</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>06rZTKMc</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>hein gauthier</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>GfQuApsR</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>ibayi christopher</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>lMOq4ljm</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>mangani thomas</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>25CTGXNp</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>quilichini ghjuvanni</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>65tYpdtq</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>santelli benjamin</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>4xeKQf0n</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>strata tony</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>dfsrq39I</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>vidal clement</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>6D2EWpmi</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>asoro joel</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>YaVQrOB5</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>colin maxime</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>the0sPaa</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>elisor simon</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>W6Zv9LTG</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>abou lo</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>tCw122Zu</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>oukidja alexandre</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>EX50xRu9</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>toure alpha</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>bDzafVGR</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>van den kerkhof kevin ali guitoune</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>GfQuApsR</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>ibayi christopher</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>GfQuApsR</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>ibayi christopher</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>CtZ04TjI</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>soumano moussa</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>65tYpdtq</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>santelli benjamin</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>65tYpdtq</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>santelli benjamin</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>4Ug33NLF</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>anziani julien</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>vXAsoH78</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>puch herrantz mehdi</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>MT98e48G</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>jabol folcarelli tim</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>4xeKQf0n</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>strata tony</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>4xeKQf0n</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>strata tony</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>dOX2dgkB</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>toure ben</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>lMOq4ljm</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>mangani thomas</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>lMOq4ljm</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>mangani thomas</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>KrAz4afq</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>junior everson</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>tCw122Zu</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>oukidja alexandre</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>tCw122Zu</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>oukidja alexandre</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>OADbJzj2</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>sy pape</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>YaVQrOB5</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>colin maxime</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>YaVQrOB5</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>colin maxime</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>ncoSpPJ3</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>kouao koffi</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>6D2EWpmi</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>asoro joel</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>6D2EWpmi</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>asoro joel</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>E5Ot0kk3</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>sabaly cheikh tidiane</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>EX50xRu9</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>toure alpha</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>EX50xRu9</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>toure alpha</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>GlPxp8Ek</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>deminguet jessy</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>the0sPaa</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>elisor simon</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>the0sPaa</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>elisor simon</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>UqhfTgL6</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>bokele mputu morgan</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>WCC14cm0</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>kouassi arsene</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>S8m3Z0Ec</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>touzghar yoann</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>